--- a/research/traditional_assets/database/data/belgium/belgium_machinery.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_machinery.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09875159672360383</v>
+        <v>0.09853846773179481</v>
       </c>
       <c r="C2">
-        <v>464.0110541575666</v>
+        <v>460.5545473560062</v>
       </c>
       <c r="D2">
-        <v>418.2110541575666</v>
+        <v>419.4955473560062</v>
       </c>
       <c r="E2">
-        <v>-49.4</v>
+        <v>-44.659</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.741</v>
       </c>
       <c r="G2">
         <v>45.8</v>
@@ -1451,28 +1451,28 @@
         <v>41.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2384723</v>
       </c>
       <c r="N2">
-        <v>41.7</v>
+        <v>41.4615277</v>
       </c>
       <c r="O2">
-        <v>10.425</v>
+        <v>10.365381925</v>
       </c>
       <c r="P2">
-        <v>31.275</v>
+        <v>31.096145775</v>
       </c>
       <c r="Q2">
-        <v>42.075</v>
+        <v>41.89614577500001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09875159672360383</v>
+        <v>0.09915274518363112</v>
       </c>
       <c r="T2">
-        <v>1.032125178898191</v>
+        <v>1.039944309041359</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>174.8630763405226</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09853846773179481</v>
+        <v>0.09832533873998581</v>
       </c>
       <c r="C3">
-        <v>460.5545473560062</v>
+        <v>457.1059552470142</v>
       </c>
       <c r="D3">
-        <v>419.4955473560062</v>
+        <v>420.7879552470142</v>
       </c>
       <c r="E3">
-        <v>-44.659</v>
+        <v>-39.918</v>
       </c>
       <c r="F3">
-        <v>4.741</v>
+        <v>9.481999999999999</v>
       </c>
       <c r="G3">
         <v>45.8</v>
@@ -1533,28 +1533,28 @@
         <v>41.7</v>
       </c>
       <c r="M3">
-        <v>0.2384723</v>
+        <v>0.4769445999999999</v>
       </c>
       <c r="N3">
-        <v>41.4615277</v>
+        <v>41.2230554</v>
       </c>
       <c r="O3">
-        <v>10.365381925</v>
+        <v>10.30576385</v>
       </c>
       <c r="P3">
-        <v>31.096145775</v>
+        <v>30.91729155</v>
       </c>
       <c r="Q3">
-        <v>41.89614577500001</v>
+        <v>41.71729155</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09915274518363112</v>
+        <v>0.09956208034692429</v>
       </c>
       <c r="T3">
-        <v>1.039944309041359</v>
+        <v>1.047923013269082</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>174.8630763405226</v>
+        <v>87.43153817026129</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09832533873998581</v>
+        <v>0.09811220974817679</v>
       </c>
       <c r="C4">
-        <v>457.1059552470142</v>
+        <v>453.6653512088861</v>
       </c>
       <c r="D4">
-        <v>420.7879552470142</v>
+        <v>422.0883512088861</v>
       </c>
       <c r="E4">
-        <v>-39.918</v>
+        <v>-35.177</v>
       </c>
       <c r="F4">
-        <v>9.481999999999999</v>
+        <v>14.223</v>
       </c>
       <c r="G4">
         <v>45.8</v>
@@ -1615,28 +1615,28 @@
         <v>41.7</v>
       </c>
       <c r="M4">
-        <v>0.4769445999999999</v>
+        <v>0.7154168999999999</v>
       </c>
       <c r="N4">
-        <v>41.2230554</v>
+        <v>40.9845831</v>
       </c>
       <c r="O4">
-        <v>10.30576385</v>
+        <v>10.246145775</v>
       </c>
       <c r="P4">
-        <v>30.91729155</v>
+        <v>30.738437325</v>
       </c>
       <c r="Q4">
-        <v>41.71729155</v>
+        <v>41.538437325</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09956208034692429</v>
+        <v>0.09997985541049154</v>
       </c>
       <c r="T4">
-        <v>1.047923013269082</v>
+        <v>1.056066226862324</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>87.43153817026129</v>
+        <v>58.28769211350753</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09811220974817679</v>
+        <v>0.09789908075636777</v>
       </c>
       <c r="C5">
-        <v>453.6653512088861</v>
+        <v>450.2328095297969</v>
       </c>
       <c r="D5">
-        <v>422.0883512088861</v>
+        <v>423.3968095297969</v>
       </c>
       <c r="E5">
-        <v>-35.177</v>
+        <v>-30.436</v>
       </c>
       <c r="F5">
-        <v>14.223</v>
+        <v>18.964</v>
       </c>
       <c r="G5">
         <v>45.8</v>
@@ -1697,28 +1697,28 @@
         <v>41.7</v>
       </c>
       <c r="M5">
-        <v>0.7154168999999999</v>
+        <v>0.9538891999999999</v>
       </c>
       <c r="N5">
-        <v>40.9845831</v>
+        <v>40.7461108</v>
       </c>
       <c r="O5">
-        <v>10.246145775</v>
+        <v>10.1865277</v>
       </c>
       <c r="P5">
-        <v>30.738437325</v>
+        <v>30.5595831</v>
       </c>
       <c r="Q5">
-        <v>41.538437325</v>
+        <v>41.35958310000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09997985541049154</v>
+        <v>0.1004063341212164</v>
       </c>
       <c r="T5">
-        <v>1.056066226862324</v>
+        <v>1.06437909073876</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>58.28769211350753</v>
+        <v>43.71576908513065</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09789908075636777</v>
+        <v>0.09768595176455878</v>
       </c>
       <c r="C6">
-        <v>450.2328095297969</v>
+        <v>446.8084054219484</v>
       </c>
       <c r="D6">
-        <v>423.3968095297969</v>
+        <v>424.7134054219484</v>
       </c>
       <c r="E6">
-        <v>-30.436</v>
+        <v>-25.695</v>
       </c>
       <c r="F6">
-        <v>18.964</v>
+        <v>23.705</v>
       </c>
       <c r="G6">
         <v>45.8</v>
@@ -1779,28 +1779,28 @@
         <v>41.7</v>
       </c>
       <c r="M6">
-        <v>0.9538891999999999</v>
+        <v>1.1923615</v>
       </c>
       <c r="N6">
-        <v>40.7461108</v>
+        <v>40.50763850000001</v>
       </c>
       <c r="O6">
-        <v>10.1865277</v>
+        <v>10.126909625</v>
       </c>
       <c r="P6">
-        <v>30.5595831</v>
+        <v>30.380728875</v>
       </c>
       <c r="Q6">
-        <v>41.35958310000001</v>
+        <v>41.180728875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1004063341212164</v>
+        <v>0.1008417913311145</v>
       </c>
       <c r="T6">
-        <v>1.06437909073876</v>
+        <v>1.072866962275751</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.71576908513065</v>
+        <v>34.97261526810452</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09768595176455878</v>
+        <v>0.09747282277274977</v>
       </c>
       <c r="C7">
-        <v>446.8084054219484</v>
+        <v>443.3922150359815</v>
       </c>
       <c r="D7">
-        <v>424.7134054219484</v>
+        <v>426.0382150359815</v>
       </c>
       <c r="E7">
-        <v>-25.695</v>
+        <v>-20.954</v>
       </c>
       <c r="F7">
-        <v>23.705</v>
+        <v>28.446</v>
       </c>
       <c r="G7">
         <v>45.8</v>
@@ -1861,28 +1861,28 @@
         <v>41.7</v>
       </c>
       <c r="M7">
-        <v>1.1923615</v>
+        <v>1.4308338</v>
       </c>
       <c r="N7">
-        <v>40.50763850000001</v>
+        <v>40.2691662</v>
       </c>
       <c r="O7">
-        <v>10.126909625</v>
+        <v>10.06729155</v>
       </c>
       <c r="P7">
-        <v>30.380728875</v>
+        <v>30.20187465</v>
       </c>
       <c r="Q7">
-        <v>41.180728875</v>
+        <v>41.00187465</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1008417913311145</v>
+        <v>0.1012865135880317</v>
       </c>
       <c r="T7">
-        <v>1.072866962275751</v>
+        <v>1.081535426824168</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.97261526810452</v>
+        <v>29.14384605675376</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09747282277274977</v>
+        <v>0.09725969378094076</v>
       </c>
       <c r="C8">
-        <v>443.3922150359815</v>
+        <v>439.984315475657</v>
       </c>
       <c r="D8">
-        <v>426.0382150359815</v>
+        <v>427.371315475657</v>
       </c>
       <c r="E8">
-        <v>-20.954</v>
+        <v>-16.213</v>
       </c>
       <c r="F8">
-        <v>28.446</v>
+        <v>33.187</v>
       </c>
       <c r="G8">
         <v>45.8</v>
@@ -1943,28 +1943,28 @@
         <v>41.7</v>
       </c>
       <c r="M8">
-        <v>1.4308338</v>
+        <v>1.6693061</v>
       </c>
       <c r="N8">
-        <v>40.2691662</v>
+        <v>40.0306939</v>
       </c>
       <c r="O8">
-        <v>10.06729155</v>
+        <v>10.007673475</v>
       </c>
       <c r="P8">
-        <v>30.20187465</v>
+        <v>30.023020425</v>
       </c>
       <c r="Q8">
-        <v>41.00187465</v>
+        <v>40.823020425</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1012865135880317</v>
+        <v>0.1017407997644524</v>
       </c>
       <c r="T8">
-        <v>1.081535426824168</v>
+        <v>1.090390309965025</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.14384605675377</v>
+        <v>24.98043947721752</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09725969378094076</v>
+        <v>0.09704656478913176</v>
       </c>
       <c r="C9">
-        <v>439.984315475657</v>
+        <v>436.5847848128154</v>
       </c>
       <c r="D9">
-        <v>427.371315475657</v>
+        <v>428.7127848128154</v>
       </c>
       <c r="E9">
-        <v>-16.213</v>
+        <v>-11.472</v>
       </c>
       <c r="F9">
-        <v>33.187</v>
+        <v>37.928</v>
       </c>
       <c r="G9">
         <v>45.8</v>
@@ -2025,28 +2025,28 @@
         <v>41.7</v>
       </c>
       <c r="M9">
-        <v>1.6693061</v>
+        <v>1.9077784</v>
       </c>
       <c r="N9">
-        <v>40.0306939</v>
+        <v>39.7922216</v>
       </c>
       <c r="O9">
-        <v>10.007673475</v>
+        <v>9.948055400000001</v>
       </c>
       <c r="P9">
-        <v>30.023020425</v>
+        <v>29.8441662</v>
       </c>
       <c r="Q9">
-        <v>40.823020425</v>
+        <v>40.6441662</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1017407997644524</v>
+        <v>0.1022049617273171</v>
       </c>
       <c r="T9">
-        <v>1.090390309965025</v>
+        <v>1.099437690565465</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.98043947721752</v>
+        <v>21.85788454256533</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09704656478913176</v>
+        <v>0.09683343579732274</v>
       </c>
       <c r="C10">
-        <v>436.5847848128154</v>
+        <v>433.1937021026179</v>
       </c>
       <c r="D10">
-        <v>428.7127848128154</v>
+        <v>430.0627021026178</v>
       </c>
       <c r="E10">
-        <v>-11.472</v>
+        <v>-6.731000000000002</v>
       </c>
       <c r="F10">
-        <v>37.928</v>
+        <v>42.669</v>
       </c>
       <c r="G10">
         <v>45.8</v>
@@ -2107,28 +2107,28 @@
         <v>41.7</v>
       </c>
       <c r="M10">
-        <v>1.9077784</v>
+        <v>2.1462507</v>
       </c>
       <c r="N10">
-        <v>39.7922216</v>
+        <v>39.5537493</v>
       </c>
       <c r="O10">
-        <v>9.948055400000001</v>
+        <v>9.888437325</v>
       </c>
       <c r="P10">
-        <v>29.8441662</v>
+        <v>29.665311975</v>
       </c>
       <c r="Q10">
-        <v>40.6441662</v>
+        <v>40.46531197500001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1022049617273171</v>
+        <v>0.102679325052003</v>
       </c>
       <c r="T10">
-        <v>1.099437690565465</v>
+        <v>1.108683914695584</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.85788454256533</v>
+        <v>19.42923070450251</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09683343579732274</v>
+        <v>0.09662030680551371</v>
       </c>
       <c r="C11">
-        <v>433.1937021026179</v>
+        <v>429.8111473990761</v>
       </c>
       <c r="D11">
-        <v>430.0627021026178</v>
+        <v>431.4211473990761</v>
       </c>
       <c r="E11">
-        <v>-6.731000000000002</v>
+        <v>-1.990000000000009</v>
       </c>
       <c r="F11">
-        <v>42.669</v>
+        <v>47.40999999999999</v>
       </c>
       <c r="G11">
         <v>45.8</v>
@@ -2189,28 +2189,28 @@
         <v>41.7</v>
       </c>
       <c r="M11">
-        <v>2.1462507</v>
+        <v>2.384722999999999</v>
       </c>
       <c r="N11">
-        <v>39.5537493</v>
+        <v>39.315277</v>
       </c>
       <c r="O11">
-        <v>9.888437325</v>
+        <v>9.82881925</v>
       </c>
       <c r="P11">
-        <v>29.665311975</v>
+        <v>29.48645775</v>
       </c>
       <c r="Q11">
-        <v>40.46531197500001</v>
+        <v>40.28645775</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.102679325052003</v>
+        <v>0.1031642297839041</v>
       </c>
       <c r="T11">
-        <v>1.108683914695584</v>
+        <v>1.11813561047304</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.42923070450251</v>
+        <v>17.48630763405226</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09662030680551371</v>
+        <v>0.09640717781370471</v>
       </c>
       <c r="C12">
-        <v>429.811147399076</v>
+        <v>426.4372017708776</v>
       </c>
       <c r="D12">
-        <v>431.4211473990761</v>
+        <v>432.7882017708776</v>
       </c>
       <c r="E12">
-        <v>-1.990000000000002</v>
+        <v>2.750999999999998</v>
       </c>
       <c r="F12">
-        <v>47.41</v>
+        <v>52.151</v>
       </c>
       <c r="G12">
         <v>45.8</v>
@@ -2271,28 +2271,28 @@
         <v>41.7</v>
       </c>
       <c r="M12">
-        <v>2.384723</v>
+        <v>2.6231953</v>
       </c>
       <c r="N12">
-        <v>39.315277</v>
+        <v>39.0768047</v>
       </c>
       <c r="O12">
-        <v>9.82881925</v>
+        <v>9.769201175000001</v>
       </c>
       <c r="P12">
-        <v>29.48645775</v>
+        <v>29.307603525</v>
       </c>
       <c r="Q12">
-        <v>40.28645775</v>
+        <v>40.107603525</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1031642297839041</v>
+        <v>0.1036600312513536</v>
       </c>
       <c r="T12">
-        <v>1.11813561047304</v>
+        <v>1.127799703908417</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.48630763405226</v>
+        <v>15.89664330368387</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09640717781370471</v>
+        <v>0.09619404882189571</v>
       </c>
       <c r="C13">
-        <v>426.4372017708776</v>
+        <v>423.0719473175139</v>
       </c>
       <c r="D13">
-        <v>432.7882017708776</v>
+        <v>434.1639473175139</v>
       </c>
       <c r="E13">
-        <v>2.750999999999998</v>
+        <v>7.491999999999997</v>
       </c>
       <c r="F13">
-        <v>52.151</v>
+        <v>56.892</v>
       </c>
       <c r="G13">
         <v>45.8</v>
@@ -2353,28 +2353,28 @@
         <v>41.7</v>
       </c>
       <c r="M13">
-        <v>2.6231953</v>
+        <v>2.8616676</v>
       </c>
       <c r="N13">
-        <v>39.0768047</v>
+        <v>38.83833240000001</v>
       </c>
       <c r="O13">
-        <v>9.769201175000001</v>
+        <v>9.709583100000001</v>
       </c>
       <c r="P13">
-        <v>29.307603525</v>
+        <v>29.1287493</v>
       </c>
       <c r="Q13">
-        <v>40.107603525</v>
+        <v>39.92874930000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1036600312513536</v>
+        <v>0.1041671009339724</v>
       </c>
       <c r="T13">
-        <v>1.127799703908417</v>
+        <v>1.137683435830961</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.89664330368387</v>
+        <v>14.57192302837688</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09619404882189571</v>
+        <v>0.09598091983008671</v>
       </c>
       <c r="C14">
-        <v>423.0719473175139</v>
+        <v>419.7154671857156</v>
       </c>
       <c r="D14">
-        <v>434.1639473175139</v>
+        <v>435.5484671857155</v>
       </c>
       <c r="E14">
-        <v>7.491999999999997</v>
+        <v>12.233</v>
       </c>
       <c r="F14">
-        <v>56.892</v>
+        <v>61.633</v>
       </c>
       <c r="G14">
         <v>45.8</v>
@@ -2435,28 +2435,28 @@
         <v>41.7</v>
       </c>
       <c r="M14">
-        <v>2.8616676</v>
+        <v>3.1001399</v>
       </c>
       <c r="N14">
-        <v>38.83833240000001</v>
+        <v>38.5998601</v>
       </c>
       <c r="O14">
-        <v>9.709583100000001</v>
+        <v>9.649965025</v>
       </c>
       <c r="P14">
-        <v>29.1287493</v>
+        <v>28.949895075</v>
       </c>
       <c r="Q14">
-        <v>39.92874930000001</v>
+        <v>39.749895075</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1041671009339724</v>
+        <v>0.1046858273909043</v>
       </c>
       <c r="T14">
-        <v>1.137683435830961</v>
+        <v>1.147794379981609</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.57192302837688</v>
+        <v>13.45100587234789</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09598091983008671</v>
+        <v>0.09592529083827769</v>
       </c>
       <c r="C15">
-        <v>419.7154671857156</v>
+        <v>415.3372963741989</v>
       </c>
       <c r="D15">
-        <v>435.5484671857155</v>
+        <v>435.9112963741989</v>
       </c>
       <c r="E15">
-        <v>12.233</v>
+        <v>16.974</v>
       </c>
       <c r="F15">
-        <v>61.633</v>
+        <v>66.374</v>
       </c>
       <c r="G15">
         <v>45.8</v>
@@ -2517,45 +2517,45 @@
         <v>41.7</v>
       </c>
       <c r="M15">
-        <v>3.1001399</v>
+        <v>3.4381732</v>
       </c>
       <c r="N15">
-        <v>38.5998601</v>
+        <v>38.2618268</v>
       </c>
       <c r="O15">
-        <v>9.649965025</v>
+        <v>9.5654567</v>
       </c>
       <c r="P15">
-        <v>28.949895075</v>
+        <v>28.6963701</v>
       </c>
       <c r="Q15">
-        <v>39.749895075</v>
+        <v>39.49637010000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1046858273909043</v>
+        <v>0.1052166172538113</v>
       </c>
       <c r="T15">
-        <v>1.147794379981609</v>
+        <v>1.158140462368319</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.45100587234789</v>
+        <v>12.12853383884209</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09592529083827769</v>
+        <v>0.09572341184646868</v>
       </c>
       <c r="C16">
-        <v>415.3372963741989</v>
+        <v>411.9181053701327</v>
       </c>
       <c r="D16">
-        <v>435.9112963741989</v>
+        <v>437.2331053701326</v>
       </c>
       <c r="E16">
-        <v>16.974</v>
+        <v>21.71500000000001</v>
       </c>
       <c r="F16">
-        <v>66.374</v>
+        <v>71.11500000000001</v>
       </c>
       <c r="G16">
         <v>45.8</v>
@@ -2599,28 +2599,28 @@
         <v>41.7</v>
       </c>
       <c r="M16">
-        <v>3.4381732</v>
+        <v>3.683757</v>
       </c>
       <c r="N16">
-        <v>38.2618268</v>
+        <v>38.016243</v>
       </c>
       <c r="O16">
-        <v>9.5654567</v>
+        <v>9.504060750000001</v>
       </c>
       <c r="P16">
-        <v>28.6963701</v>
+        <v>28.51218225</v>
       </c>
       <c r="Q16">
-        <v>39.49637010000001</v>
+        <v>39.31218225000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1052166172538113</v>
+        <v>0.1057598962899632</v>
       </c>
       <c r="T16">
-        <v>1.158140462368319</v>
+        <v>1.168729981987658</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.12853383884209</v>
+        <v>11.31996491625262</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09572341184646868</v>
+        <v>0.09552153285465967</v>
       </c>
       <c r="C17">
-        <v>411.9181053701327</v>
+        <v>408.5069549610301</v>
       </c>
       <c r="D17">
-        <v>437.2331053701326</v>
+        <v>438.5629549610301</v>
       </c>
       <c r="E17">
-        <v>21.715</v>
+        <v>26.456</v>
       </c>
       <c r="F17">
-        <v>71.11499999999999</v>
+        <v>75.85599999999999</v>
       </c>
       <c r="G17">
         <v>45.8</v>
@@ -2681,28 +2681,28 @@
         <v>41.7</v>
       </c>
       <c r="M17">
-        <v>3.683757</v>
+        <v>3.929340799999999</v>
       </c>
       <c r="N17">
-        <v>38.016243</v>
+        <v>37.7706592</v>
       </c>
       <c r="O17">
-        <v>9.504060750000001</v>
+        <v>9.442664800000001</v>
       </c>
       <c r="P17">
-        <v>28.51218225</v>
+        <v>28.3279944</v>
       </c>
       <c r="Q17">
-        <v>39.31218225000001</v>
+        <v>39.12799440000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1057598962899632</v>
+        <v>0.1063161105412615</v>
       </c>
       <c r="T17">
-        <v>1.168729981987658</v>
+        <v>1.179571633026504</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.31996491625262</v>
+        <v>10.61246710898683</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09552153285465967</v>
+        <v>0.09531965386285067</v>
       </c>
       <c r="C18">
-        <v>408.5069549610301</v>
+        <v>405.1039187374076</v>
       </c>
       <c r="D18">
-        <v>438.5629549610301</v>
+        <v>439.9009187374076</v>
       </c>
       <c r="E18">
-        <v>26.456</v>
+        <v>31.197</v>
       </c>
       <c r="F18">
-        <v>75.85599999999999</v>
+        <v>80.59699999999999</v>
       </c>
       <c r="G18">
         <v>45.8</v>
@@ -2763,28 +2763,28 @@
         <v>41.7</v>
       </c>
       <c r="M18">
-        <v>3.929340799999999</v>
+        <v>4.1749246</v>
       </c>
       <c r="N18">
-        <v>37.7706592</v>
+        <v>37.52507540000001</v>
       </c>
       <c r="O18">
-        <v>9.442664800000001</v>
+        <v>9.381268850000001</v>
       </c>
       <c r="P18">
-        <v>28.3279944</v>
+        <v>28.14380655</v>
       </c>
       <c r="Q18">
-        <v>39.12799440000001</v>
+        <v>38.94380655000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1063161105412615</v>
+        <v>0.1068857275456032</v>
       </c>
       <c r="T18">
-        <v>1.179571633026504</v>
+        <v>1.190674528668697</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.61246710898683</v>
+        <v>9.988204337869959</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09531965386285067</v>
+        <v>0.09534727487104165</v>
       </c>
       <c r="C19">
-        <v>405.1039187374076</v>
+        <v>400.1793771685822</v>
       </c>
       <c r="D19">
-        <v>439.9009187374076</v>
+        <v>439.7173771685822</v>
       </c>
       <c r="E19">
-        <v>31.197</v>
+        <v>35.93800000000001</v>
       </c>
       <c r="F19">
-        <v>80.59699999999999</v>
+        <v>85.33800000000001</v>
       </c>
       <c r="G19">
         <v>45.8</v>
@@ -2845,45 +2845,45 @@
         <v>41.7</v>
       </c>
       <c r="M19">
-        <v>4.1749246</v>
+        <v>4.565583</v>
       </c>
       <c r="N19">
-        <v>37.52507540000001</v>
+        <v>37.134417</v>
       </c>
       <c r="O19">
-        <v>9.381268850000001</v>
+        <v>9.28360425</v>
       </c>
       <c r="P19">
-        <v>28.14380655</v>
+        <v>27.85081275</v>
       </c>
       <c r="Q19">
-        <v>38.94380655000001</v>
+        <v>38.65081275</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1068857275456032</v>
+        <v>0.1074692376476118</v>
       </c>
       <c r="T19">
-        <v>1.190674528668697</v>
+        <v>1.202048226643625</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.988204337869959</v>
+        <v>9.133554247069871</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09534727487104167</v>
+        <v>0.09515814587923264</v>
       </c>
       <c r="C20">
-        <v>400.1793771685822</v>
+        <v>396.6982139995703</v>
       </c>
       <c r="D20">
-        <v>439.7173771685822</v>
+        <v>440.9772139995703</v>
       </c>
       <c r="E20">
-        <v>35.938</v>
+        <v>40.67899999999999</v>
       </c>
       <c r="F20">
-        <v>85.33799999999999</v>
+        <v>90.07899999999999</v>
       </c>
       <c r="G20">
         <v>45.8</v>
@@ -2927,28 +2927,28 @@
         <v>41.7</v>
       </c>
       <c r="M20">
-        <v>4.565582999999999</v>
+        <v>4.819226499999999</v>
       </c>
       <c r="N20">
-        <v>37.13441700000001</v>
+        <v>36.8807735</v>
       </c>
       <c r="O20">
-        <v>9.283604250000002</v>
+        <v>9.220193375000001</v>
       </c>
       <c r="P20">
-        <v>27.85081275</v>
+        <v>27.660580125</v>
       </c>
       <c r="Q20">
-        <v>38.65081275</v>
+        <v>38.46058012500001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1074692376476118</v>
+        <v>0.1080671554064601</v>
       </c>
       <c r="T20">
-        <v>1.202048226643625</v>
+        <v>1.213702756667318</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.133554247069872</v>
+        <v>8.652840865645143</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09515814587923264</v>
+        <v>0.09496901688742365</v>
       </c>
       <c r="C21">
-        <v>396.6982139995703</v>
+        <v>393.2242907053223</v>
       </c>
       <c r="D21">
-        <v>440.9772139995703</v>
+        <v>442.2442907053223</v>
       </c>
       <c r="E21">
-        <v>40.67899999999999</v>
+        <v>45.41999999999999</v>
       </c>
       <c r="F21">
-        <v>90.07899999999999</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G21">
         <v>45.8</v>
@@ -3009,28 +3009,28 @@
         <v>41.7</v>
       </c>
       <c r="M21">
-        <v>4.819226499999999</v>
+        <v>5.072869999999999</v>
       </c>
       <c r="N21">
-        <v>36.8807735</v>
+        <v>36.62713</v>
       </c>
       <c r="O21">
-        <v>9.220193375000001</v>
+        <v>9.1567825</v>
       </c>
       <c r="P21">
-        <v>27.660580125</v>
+        <v>27.4703475</v>
       </c>
       <c r="Q21">
-        <v>38.46058012500001</v>
+        <v>38.2703475</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1080671554064601</v>
+        <v>0.1086800211092795</v>
       </c>
       <c r="T21">
-        <v>1.213702756667318</v>
+        <v>1.225648649941602</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.652840865645143</v>
+        <v>8.220198822362885</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09496901688742365</v>
+        <v>0.09477988789561462</v>
       </c>
       <c r="C22">
-        <v>393.2242907053223</v>
+        <v>389.757669873502</v>
       </c>
       <c r="D22">
-        <v>442.2442907053223</v>
+        <v>443.518669873502</v>
       </c>
       <c r="E22">
-        <v>45.41999999999999</v>
+        <v>50.16100000000001</v>
       </c>
       <c r="F22">
-        <v>94.81999999999999</v>
+        <v>99.56100000000001</v>
       </c>
       <c r="G22">
         <v>45.8</v>
@@ -3091,28 +3091,28 @@
         <v>41.7</v>
       </c>
       <c r="M22">
-        <v>5.072869999999999</v>
+        <v>5.3265135</v>
       </c>
       <c r="N22">
-        <v>36.62713</v>
+        <v>36.37348650000001</v>
       </c>
       <c r="O22">
-        <v>9.1567825</v>
+        <v>9.093371625000001</v>
       </c>
       <c r="P22">
-        <v>27.4703475</v>
+        <v>27.280114875</v>
       </c>
       <c r="Q22">
-        <v>38.2703475</v>
+        <v>38.08011487500001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1086800211092795</v>
+        <v>0.1093084023995122</v>
       </c>
       <c r="T22">
-        <v>1.225648649941602</v>
+        <v>1.237896970893716</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.220198822362885</v>
+        <v>7.828760783202747</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09477988789561462</v>
+        <v>0.09472275890380562</v>
       </c>
       <c r="C23">
-        <v>389.757669873502</v>
+        <v>385.4030590705853</v>
       </c>
       <c r="D23">
-        <v>443.518669873502</v>
+        <v>443.9050590705853</v>
       </c>
       <c r="E23">
-        <v>50.16099999999999</v>
+        <v>54.90199999999999</v>
       </c>
       <c r="F23">
-        <v>99.56099999999999</v>
+        <v>104.302</v>
       </c>
       <c r="G23">
         <v>45.8</v>
@@ -3173,45 +3173,45 @@
         <v>41.7</v>
       </c>
       <c r="M23">
-        <v>5.3265135</v>
+        <v>5.663598599999999</v>
       </c>
       <c r="N23">
-        <v>36.37348650000001</v>
+        <v>36.0364014</v>
       </c>
       <c r="O23">
-        <v>9.093371625000001</v>
+        <v>9.009100350000001</v>
       </c>
       <c r="P23">
-        <v>27.280114875</v>
+        <v>27.02730105</v>
       </c>
       <c r="Q23">
-        <v>38.08011487500001</v>
+        <v>37.82730105</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1093084023995122</v>
+        <v>0.10995289603052</v>
       </c>
       <c r="T23">
-        <v>1.237896970893716</v>
+        <v>1.250459351357424</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.828760783202747</v>
+        <v>7.362809927949344</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09472275890380562</v>
+        <v>0.0945396299119966</v>
       </c>
       <c r="C24">
-        <v>385.4030590705853</v>
+        <v>381.9051938865676</v>
       </c>
       <c r="D24">
-        <v>443.9050590705853</v>
+        <v>445.1481938865676</v>
       </c>
       <c r="E24">
-        <v>54.90199999999999</v>
+        <v>59.64299999999999</v>
       </c>
       <c r="F24">
-        <v>104.302</v>
+        <v>109.043</v>
       </c>
       <c r="G24">
         <v>45.8</v>
@@ -3255,28 +3255,28 @@
         <v>41.7</v>
       </c>
       <c r="M24">
-        <v>5.663598599999999</v>
+        <v>5.9210349</v>
       </c>
       <c r="N24">
-        <v>36.0364014</v>
+        <v>35.7789651</v>
       </c>
       <c r="O24">
-        <v>9.009100350000001</v>
+        <v>8.944741275</v>
       </c>
       <c r="P24">
-        <v>27.02730105</v>
+        <v>26.834223825</v>
       </c>
       <c r="Q24">
-        <v>37.82730105</v>
+        <v>37.63422382500001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.10995289603052</v>
+        <v>0.1106141297558398</v>
       </c>
       <c r="T24">
-        <v>1.250459351357424</v>
+        <v>1.263348027417591</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.362809927949344</v>
+        <v>7.042687757168937</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0945396299119966</v>
+        <v>0.0943565009201876</v>
       </c>
       <c r="C25">
-        <v>381.9051938865676</v>
+        <v>378.4143109347503</v>
       </c>
       <c r="D25">
-        <v>445.1481938865676</v>
+        <v>446.3983109347503</v>
       </c>
       <c r="E25">
-        <v>59.64299999999999</v>
+        <v>64.38400000000001</v>
       </c>
       <c r="F25">
-        <v>109.043</v>
+        <v>113.784</v>
       </c>
       <c r="G25">
         <v>45.8</v>
@@ -3337,28 +3337,28 @@
         <v>41.7</v>
       </c>
       <c r="M25">
-        <v>5.9210349</v>
+        <v>6.178471200000001</v>
       </c>
       <c r="N25">
-        <v>35.7789651</v>
+        <v>35.5215288</v>
       </c>
       <c r="O25">
-        <v>8.944741275</v>
+        <v>8.8803822</v>
       </c>
       <c r="P25">
-        <v>26.834223825</v>
+        <v>26.6411466</v>
       </c>
       <c r="Q25">
-        <v>37.63422382500001</v>
+        <v>37.4411466</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1106141297558398</v>
+        <v>0.1112927643686679</v>
       </c>
       <c r="T25">
-        <v>1.263348027417591</v>
+        <v>1.276575879163552</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.042687757168937</v>
+        <v>6.749242433953563</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0943565009201876</v>
+        <v>0.09417337192837857</v>
       </c>
       <c r="C26">
-        <v>378.4143109347503</v>
+        <v>374.9304692057531</v>
       </c>
       <c r="D26">
-        <v>446.3983109347503</v>
+        <v>447.655469205753</v>
       </c>
       <c r="E26">
-        <v>64.38399999999999</v>
+        <v>69.125</v>
       </c>
       <c r="F26">
-        <v>113.784</v>
+        <v>118.525</v>
       </c>
       <c r="G26">
         <v>45.8</v>
@@ -3419,28 +3419,28 @@
         <v>41.7</v>
       </c>
       <c r="M26">
-        <v>6.1784712</v>
+        <v>6.4359075</v>
       </c>
       <c r="N26">
-        <v>35.52152880000001</v>
+        <v>35.2640925</v>
       </c>
       <c r="O26">
-        <v>8.880382200000001</v>
+        <v>8.816023125000001</v>
       </c>
       <c r="P26">
-        <v>26.64114660000001</v>
+        <v>26.448069375</v>
       </c>
       <c r="Q26">
-        <v>37.44114660000001</v>
+        <v>37.248069375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1112927643686679</v>
+        <v>0.1119894959045048</v>
       </c>
       <c r="T26">
-        <v>1.276575879163552</v>
+        <v>1.290156473622739</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.749242433953565</v>
+        <v>6.479272736595423</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09417337192837857</v>
+        <v>0.09399024293656959</v>
       </c>
       <c r="C27">
-        <v>374.9304692057531</v>
+        <v>371.4537283565951</v>
       </c>
       <c r="D27">
-        <v>447.655469205753</v>
+        <v>448.919728356595</v>
       </c>
       <c r="E27">
-        <v>69.125</v>
+        <v>73.86599999999999</v>
       </c>
       <c r="F27">
-        <v>118.525</v>
+        <v>123.266</v>
       </c>
       <c r="G27">
         <v>45.8</v>
@@ -3501,28 +3501,28 @@
         <v>41.7</v>
       </c>
       <c r="M27">
-        <v>6.4359075</v>
+        <v>6.6933438</v>
       </c>
       <c r="N27">
-        <v>35.2640925</v>
+        <v>35.0066562</v>
       </c>
       <c r="O27">
-        <v>8.816023125000001</v>
+        <v>8.75166405</v>
       </c>
       <c r="P27">
-        <v>26.448069375</v>
+        <v>26.25499215</v>
       </c>
       <c r="Q27">
-        <v>37.248069375</v>
+        <v>37.05499215</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1119894959045048</v>
+        <v>0.1127050580223913</v>
       </c>
       <c r="T27">
-        <v>1.290156473622739</v>
+        <v>1.304104111175417</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.479272736595423</v>
+        <v>6.23006993903406</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09399024293656959</v>
+        <v>0.09400961394476057</v>
       </c>
       <c r="C28">
-        <v>371.4537283565951</v>
+        <v>366.5786599947801</v>
       </c>
       <c r="D28">
-        <v>448.919728356595</v>
+        <v>448.7856599947801</v>
       </c>
       <c r="E28">
-        <v>73.86599999999999</v>
+        <v>78.607</v>
       </c>
       <c r="F28">
-        <v>123.266</v>
+        <v>128.007</v>
       </c>
       <c r="G28">
         <v>45.8</v>
@@ -3583,45 +3583,45 @@
         <v>41.7</v>
       </c>
       <c r="M28">
-        <v>6.6933438</v>
+        <v>7.0787871</v>
       </c>
       <c r="N28">
-        <v>35.0066562</v>
+        <v>34.6212129</v>
       </c>
       <c r="O28">
-        <v>8.75166405</v>
+        <v>8.655303225000001</v>
       </c>
       <c r="P28">
-        <v>26.25499215</v>
+        <v>25.965909675</v>
       </c>
       <c r="Q28">
-        <v>37.05499215</v>
+        <v>36.765909675</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1127050580223913</v>
+        <v>0.1134402245818638</v>
       </c>
       <c r="T28">
-        <v>1.304104111175417</v>
+        <v>1.318433875784333</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.23006993903406</v>
+        <v>5.890839689189127</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09400961394476057</v>
+        <v>0.09383398495295156</v>
       </c>
       <c r="C29">
-        <v>366.5786599947801</v>
+        <v>363.056139147899</v>
       </c>
       <c r="D29">
-        <v>448.7856599947801</v>
+        <v>450.004139147899</v>
       </c>
       <c r="E29">
-        <v>78.607</v>
+        <v>83.34799999999998</v>
       </c>
       <c r="F29">
-        <v>128.007</v>
+        <v>132.748</v>
       </c>
       <c r="G29">
         <v>45.8</v>
@@ -3665,28 +3665,28 @@
         <v>41.7</v>
       </c>
       <c r="M29">
-        <v>7.0787871</v>
+        <v>7.3409644</v>
       </c>
       <c r="N29">
-        <v>34.6212129</v>
+        <v>34.35903560000001</v>
       </c>
       <c r="O29">
-        <v>8.655303225000001</v>
+        <v>8.589758900000001</v>
       </c>
       <c r="P29">
-        <v>25.965909675</v>
+        <v>25.76927670000001</v>
       </c>
       <c r="Q29">
-        <v>36.765909675</v>
+        <v>36.5692767</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1134402245818638</v>
+        <v>0.114195812434655</v>
       </c>
       <c r="T29">
-        <v>1.318433875784333</v>
+        <v>1.333161689410164</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.890839689189127</v>
+        <v>5.680452557432373</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09383398495295156</v>
+        <v>0.09365835596114255</v>
       </c>
       <c r="C30">
-        <v>363.056139147899</v>
+        <v>359.5402527975142</v>
       </c>
       <c r="D30">
-        <v>450.004139147899</v>
+        <v>451.2292527975142</v>
       </c>
       <c r="E30">
-        <v>83.34799999999998</v>
+        <v>88.089</v>
       </c>
       <c r="F30">
-        <v>132.748</v>
+        <v>137.489</v>
       </c>
       <c r="G30">
         <v>45.8</v>
@@ -3747,28 +3747,28 @@
         <v>41.7</v>
       </c>
       <c r="M30">
-        <v>7.3409644</v>
+        <v>7.6031417</v>
       </c>
       <c r="N30">
-        <v>34.35903560000001</v>
+        <v>34.0968583</v>
       </c>
       <c r="O30">
-        <v>8.589758900000001</v>
+        <v>8.524214575</v>
       </c>
       <c r="P30">
-        <v>25.76927670000001</v>
+        <v>25.572643725</v>
       </c>
       <c r="Q30">
-        <v>36.5692767</v>
+        <v>36.372643725</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.114195812434655</v>
+        <v>0.1149726844523135</v>
       </c>
       <c r="T30">
-        <v>1.333161689410164</v>
+        <v>1.348304371025454</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.680452557432373</v>
+        <v>5.484574883038152</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09365835596114255</v>
+        <v>0.09348272696933353</v>
       </c>
       <c r="C31">
-        <v>359.5402527975143</v>
+        <v>356.0310552777977</v>
       </c>
       <c r="D31">
-        <v>451.2292527975142</v>
+        <v>452.4610552777976</v>
       </c>
       <c r="E31">
-        <v>88.08899999999997</v>
+        <v>92.82999999999998</v>
       </c>
       <c r="F31">
-        <v>137.489</v>
+        <v>142.23</v>
       </c>
       <c r="G31">
         <v>45.8</v>
@@ -3829,28 +3829,28 @@
         <v>41.7</v>
       </c>
       <c r="M31">
-        <v>7.603141699999999</v>
+        <v>7.865319</v>
       </c>
       <c r="N31">
-        <v>34.0968583</v>
+        <v>33.834681</v>
       </c>
       <c r="O31">
-        <v>8.524214575</v>
+        <v>8.458670250000001</v>
       </c>
       <c r="P31">
-        <v>25.572643725</v>
+        <v>25.37601075</v>
       </c>
       <c r="Q31">
-        <v>36.372643725</v>
+        <v>36.17601075</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1149726844523135</v>
+        <v>0.1157717528133336</v>
       </c>
       <c r="T31">
-        <v>1.348304371025454</v>
+        <v>1.363879700686895</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.484574883038153</v>
+        <v>5.301755720270215</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09348272696933353</v>
+        <v>0.09330709797752451</v>
       </c>
       <c r="C32">
-        <v>356.0310552777977</v>
+        <v>352.5286015178484</v>
       </c>
       <c r="D32">
-        <v>452.4610552777976</v>
+        <v>453.6996015178484</v>
       </c>
       <c r="E32">
-        <v>92.82999999999998</v>
+        <v>97.57099999999997</v>
       </c>
       <c r="F32">
-        <v>142.23</v>
+        <v>146.971</v>
       </c>
       <c r="G32">
         <v>45.8</v>
@@ -3911,28 +3911,28 @@
         <v>41.7</v>
       </c>
       <c r="M32">
-        <v>7.865319</v>
+        <v>8.127496299999999</v>
       </c>
       <c r="N32">
-        <v>33.834681</v>
+        <v>33.57250370000001</v>
       </c>
       <c r="O32">
-        <v>8.458670250000001</v>
+        <v>8.393125925000001</v>
       </c>
       <c r="P32">
-        <v>25.37601075</v>
+        <v>25.17937777500001</v>
       </c>
       <c r="Q32">
-        <v>36.17601075</v>
+        <v>35.979377775</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1157717528133336</v>
+        <v>0.1165939825761225</v>
       </c>
       <c r="T32">
-        <v>1.363879700686895</v>
+        <v>1.379906489179103</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.301755720270215</v>
+        <v>5.130731342196983</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09330709797752451</v>
+        <v>0.0931314689857155</v>
       </c>
       <c r="C33">
-        <v>352.5286015178484</v>
+        <v>349.0329470498583</v>
       </c>
       <c r="D33">
-        <v>453.6996015178484</v>
+        <v>454.9449470498582</v>
       </c>
       <c r="E33">
-        <v>97.57099999999997</v>
+        <v>102.312</v>
       </c>
       <c r="F33">
-        <v>146.971</v>
+        <v>151.712</v>
       </c>
       <c r="G33">
         <v>45.8</v>
@@ -3993,28 +3993,28 @@
         <v>41.7</v>
       </c>
       <c r="M33">
-        <v>8.127496299999999</v>
+        <v>8.3896736</v>
       </c>
       <c r="N33">
-        <v>33.57250370000001</v>
+        <v>33.3103264</v>
       </c>
       <c r="O33">
-        <v>8.393125925000001</v>
+        <v>8.3275816</v>
       </c>
       <c r="P33">
-        <v>25.17937777500001</v>
+        <v>24.9827448</v>
       </c>
       <c r="Q33">
-        <v>35.979377775</v>
+        <v>35.7827448</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1165939825761225</v>
+        <v>0.1174403955672287</v>
       </c>
       <c r="T33">
-        <v>1.379906489179103</v>
+        <v>1.396404653803435</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.130731342196983</v>
+        <v>4.970395987753326</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0931314689857155</v>
+        <v>0.0929558399939065</v>
       </c>
       <c r="C34">
-        <v>349.0329470498583</v>
+        <v>345.5441480174113</v>
       </c>
       <c r="D34">
-        <v>454.9449470498582</v>
+        <v>456.1971480174113</v>
       </c>
       <c r="E34">
-        <v>102.312</v>
+        <v>107.053</v>
       </c>
       <c r="F34">
-        <v>151.712</v>
+        <v>156.453</v>
       </c>
       <c r="G34">
         <v>45.8</v>
@@ -4075,28 +4075,28 @@
         <v>41.7</v>
       </c>
       <c r="M34">
-        <v>8.3896736</v>
+        <v>8.651850900000001</v>
       </c>
       <c r="N34">
-        <v>33.3103264</v>
+        <v>33.0481491</v>
       </c>
       <c r="O34">
-        <v>8.3275816</v>
+        <v>8.262037275000001</v>
       </c>
       <c r="P34">
-        <v>24.9827448</v>
+        <v>24.786111825</v>
       </c>
       <c r="Q34">
-        <v>35.7827448</v>
+        <v>35.586111825</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1174403955672287</v>
+        <v>0.1183120746177709</v>
       </c>
       <c r="T34">
-        <v>1.396404653803435</v>
+        <v>1.413395300953866</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.970395987753326</v>
+        <v>4.819777927518376</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0929558399939065</v>
+        <v>0.0927802110020975</v>
       </c>
       <c r="C35">
-        <v>345.5441480174113</v>
+        <v>342.0622611839214</v>
       </c>
       <c r="D35">
-        <v>456.1971480174113</v>
+        <v>457.4562611839214</v>
       </c>
       <c r="E35">
-        <v>107.053</v>
+        <v>111.794</v>
       </c>
       <c r="F35">
-        <v>156.453</v>
+        <v>161.194</v>
       </c>
       <c r="G35">
         <v>45.8</v>
@@ -4157,28 +4157,28 @@
         <v>41.7</v>
       </c>
       <c r="M35">
-        <v>8.651850900000001</v>
+        <v>8.914028199999999</v>
       </c>
       <c r="N35">
-        <v>33.0481491</v>
+        <v>32.78597180000001</v>
       </c>
       <c r="O35">
-        <v>8.262037275000001</v>
+        <v>8.196492950000001</v>
       </c>
       <c r="P35">
-        <v>24.786111825</v>
+        <v>24.58947885000001</v>
       </c>
       <c r="Q35">
-        <v>35.586111825</v>
+        <v>35.38947885</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1183120746177709</v>
+        <v>0.1192101681849962</v>
       </c>
       <c r="T35">
-        <v>1.413395300953866</v>
+        <v>1.430900816199765</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.819777927518376</v>
+        <v>4.678019753179601</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0927802110020975</v>
+        <v>0.09260458201028848</v>
       </c>
       <c r="C36">
-        <v>342.0622611839214</v>
+        <v>338.5873439412094</v>
       </c>
       <c r="D36">
-        <v>457.4562611839214</v>
+        <v>458.7223439412094</v>
       </c>
       <c r="E36">
-        <v>111.794</v>
+        <v>116.535</v>
       </c>
       <c r="F36">
-        <v>161.194</v>
+        <v>165.935</v>
       </c>
       <c r="G36">
         <v>45.8</v>
@@ -4239,28 +4239,28 @@
         <v>41.7</v>
       </c>
       <c r="M36">
-        <v>8.914028199999999</v>
+        <v>9.1762055</v>
       </c>
       <c r="N36">
-        <v>32.78597180000001</v>
+        <v>32.5237945</v>
       </c>
       <c r="O36">
-        <v>8.196492950000001</v>
+        <v>8.130948625</v>
       </c>
       <c r="P36">
-        <v>24.58947885000001</v>
+        <v>24.392845875</v>
       </c>
       <c r="Q36">
-        <v>35.38947885</v>
+        <v>35.192845875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1192101681849962</v>
+        <v>0.1201358954004438</v>
       </c>
       <c r="T36">
-        <v>1.430900816199765</v>
+        <v>1.448944962683999</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.678019753179601</v>
+        <v>4.544362045945897</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09260458201028848</v>
+        <v>0.09310395301847949</v>
       </c>
       <c r="C37">
-        <v>338.5873439412094</v>
+        <v>330.2646762831873</v>
       </c>
       <c r="D37">
-        <v>458.7223439412094</v>
+        <v>455.1406762831873</v>
       </c>
       <c r="E37">
-        <v>116.535</v>
+        <v>121.276</v>
       </c>
       <c r="F37">
-        <v>165.935</v>
+        <v>170.676</v>
       </c>
       <c r="G37">
         <v>45.8</v>
@@ -4321,45 +4321,45 @@
         <v>41.7</v>
       </c>
       <c r="M37">
-        <v>9.1762055</v>
+        <v>9.865072800000002</v>
       </c>
       <c r="N37">
-        <v>32.5237945</v>
+        <v>31.8349272</v>
       </c>
       <c r="O37">
-        <v>8.130948625</v>
+        <v>7.958731800000001</v>
       </c>
       <c r="P37">
-        <v>24.392845875</v>
+        <v>23.8761954</v>
       </c>
       <c r="Q37">
-        <v>35.192845875</v>
+        <v>34.6761954</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1201358954004438</v>
+        <v>0.1210905515913742</v>
       </c>
       <c r="T37">
-        <v>1.448944962683999</v>
+        <v>1.467552988745866</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.544362045945897</v>
+        <v>4.227034188739083</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09310395301847949</v>
+        <v>0.09294707402667046</v>
       </c>
       <c r="C38">
-        <v>330.2646762831873</v>
+        <v>326.6428283160151</v>
       </c>
       <c r="D38">
-        <v>455.1406762831873</v>
+        <v>456.259828316015</v>
       </c>
       <c r="E38">
-        <v>121.276</v>
+        <v>126.017</v>
       </c>
       <c r="F38">
-        <v>170.676</v>
+        <v>175.417</v>
       </c>
       <c r="G38">
         <v>45.8</v>
@@ -4403,28 +4403,28 @@
         <v>41.7</v>
       </c>
       <c r="M38">
-        <v>9.8650728</v>
+        <v>10.1391026</v>
       </c>
       <c r="N38">
-        <v>31.8349272</v>
+        <v>31.5608974</v>
       </c>
       <c r="O38">
-        <v>7.958731800000001</v>
+        <v>7.89022435</v>
       </c>
       <c r="P38">
-        <v>23.8761954</v>
+        <v>23.67067305</v>
       </c>
       <c r="Q38">
-        <v>34.6761954</v>
+        <v>34.47067305</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1210905515913742</v>
+        <v>0.1220755143280484</v>
       </c>
       <c r="T38">
-        <v>1.467552988745866</v>
+        <v>1.486751745793823</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.227034188739084</v>
+        <v>4.112790021475865</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09294707402667046</v>
+        <v>0.09279019503486147</v>
       </c>
       <c r="C39">
-        <v>326.6428283160151</v>
+        <v>323.0264977140145</v>
       </c>
       <c r="D39">
-        <v>456.259828316015</v>
+        <v>457.3844977140144</v>
       </c>
       <c r="E39">
-        <v>126.017</v>
+        <v>130.758</v>
       </c>
       <c r="F39">
-        <v>175.417</v>
+        <v>180.158</v>
       </c>
       <c r="G39">
         <v>45.8</v>
@@ -4485,28 +4485,28 @@
         <v>41.7</v>
       </c>
       <c r="M39">
-        <v>10.1391026</v>
+        <v>10.4131324</v>
       </c>
       <c r="N39">
-        <v>31.5608974</v>
+        <v>31.2868676</v>
       </c>
       <c r="O39">
-        <v>7.89022435</v>
+        <v>7.8217169</v>
       </c>
       <c r="P39">
-        <v>23.67067305</v>
+        <v>23.4651507</v>
       </c>
       <c r="Q39">
-        <v>34.47067305</v>
+        <v>34.26515070000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1220755143280484</v>
+        <v>0.1230922500562282</v>
       </c>
       <c r="T39">
-        <v>1.486751745793823</v>
+        <v>1.506569817585263</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.112790021475865</v>
+        <v>4.004558705121237</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09279019503486147</v>
+        <v>0.09365706604305246</v>
       </c>
       <c r="C40">
-        <v>323.0264977140145</v>
+        <v>312.1392753979679</v>
       </c>
       <c r="D40">
-        <v>457.3844977140144</v>
+        <v>451.2382753979679</v>
       </c>
       <c r="E40">
-        <v>130.758</v>
+        <v>135.499</v>
       </c>
       <c r="F40">
-        <v>180.158</v>
+        <v>184.899</v>
       </c>
       <c r="G40">
         <v>45.8</v>
@@ -4567,45 +4567,45 @@
         <v>41.7</v>
       </c>
       <c r="M40">
-        <v>10.4131324</v>
+        <v>11.3343087</v>
       </c>
       <c r="N40">
-        <v>31.2868676</v>
+        <v>30.3656913</v>
       </c>
       <c r="O40">
-        <v>7.8217169</v>
+        <v>7.591422825</v>
       </c>
       <c r="P40">
-        <v>23.4651507</v>
+        <v>22.774268475</v>
       </c>
       <c r="Q40">
-        <v>34.26515070000001</v>
+        <v>33.574268475</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1230922500562282</v>
+        <v>0.1241423213820532</v>
       </c>
       <c r="T40">
-        <v>1.506569817585263</v>
+        <v>1.527037662222324</v>
       </c>
       <c r="U40">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.004558705121237</v>
+        <v>3.679095135286019</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09365706604305246</v>
+        <v>0.09352643705124344</v>
       </c>
       <c r="C41">
-        <v>312.1392753979679</v>
+        <v>308.3138593307855</v>
       </c>
       <c r="D41">
-        <v>451.2382753979679</v>
+        <v>452.1538593307855</v>
       </c>
       <c r="E41">
-        <v>135.499</v>
+        <v>140.24</v>
       </c>
       <c r="F41">
-        <v>184.899</v>
+        <v>189.64</v>
       </c>
       <c r="G41">
         <v>45.8</v>
@@ -4649,28 +4649,28 @@
         <v>41.7</v>
       </c>
       <c r="M41">
-        <v>11.3343087</v>
+        <v>11.624932</v>
       </c>
       <c r="N41">
-        <v>30.3656913</v>
+        <v>30.075068</v>
       </c>
       <c r="O41">
-        <v>7.591422825</v>
+        <v>7.518767</v>
       </c>
       <c r="P41">
-        <v>22.774268475</v>
+        <v>22.556301</v>
       </c>
       <c r="Q41">
-        <v>33.574268475</v>
+        <v>33.356301</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1241423213820532</v>
+        <v>0.1252273950854057</v>
       </c>
       <c r="T41">
-        <v>1.527037662222324</v>
+        <v>1.548187768347287</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.679095135286019</v>
+        <v>3.587117756903869</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09352643705124344</v>
+        <v>0.09425680805943443</v>
       </c>
       <c r="C42">
-        <v>308.3138593307855</v>
+        <v>298.5008132971215</v>
       </c>
       <c r="D42">
-        <v>452.1538593307855</v>
+        <v>447.0818132971214</v>
       </c>
       <c r="E42">
-        <v>140.24</v>
+        <v>144.981</v>
       </c>
       <c r="F42">
-        <v>189.64</v>
+        <v>194.381</v>
       </c>
       <c r="G42">
         <v>45.8</v>
@@ -4731,45 +4731,45 @@
         <v>41.7</v>
       </c>
       <c r="M42">
-        <v>11.624932</v>
+        <v>12.4598221</v>
       </c>
       <c r="N42">
-        <v>30.075068</v>
+        <v>29.2401779</v>
       </c>
       <c r="O42">
-        <v>7.518767</v>
+        <v>7.310044475000001</v>
       </c>
       <c r="P42">
-        <v>22.556301</v>
+        <v>21.930133425</v>
       </c>
       <c r="Q42">
-        <v>33.356301</v>
+        <v>32.73013342500001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1252273950854057</v>
+        <v>0.126349250948194</v>
       </c>
       <c r="T42">
-        <v>1.548187768347287</v>
+        <v>1.570054827222249</v>
       </c>
       <c r="U42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.587117756903869</v>
+        <v>3.346757254262884</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09425680805943443</v>
+        <v>0.09414717906762543</v>
       </c>
       <c r="C43">
-        <v>298.5008132971215</v>
+        <v>294.5138590607326</v>
       </c>
       <c r="D43">
-        <v>447.0818132971214</v>
+        <v>447.8358590607326</v>
       </c>
       <c r="E43">
-        <v>144.981</v>
+        <v>149.722</v>
       </c>
       <c r="F43">
-        <v>194.381</v>
+        <v>199.122</v>
       </c>
       <c r="G43">
         <v>45.8</v>
@@ -4813,28 +4813,28 @@
         <v>41.7</v>
       </c>
       <c r="M43">
-        <v>12.4598221</v>
+        <v>12.7637202</v>
       </c>
       <c r="N43">
-        <v>29.2401779</v>
+        <v>28.9362798</v>
       </c>
       <c r="O43">
-        <v>7.310044475000001</v>
+        <v>7.23406995</v>
       </c>
       <c r="P43">
-        <v>21.930133425</v>
+        <v>21.70220985</v>
       </c>
       <c r="Q43">
-        <v>32.73013342500001</v>
+        <v>32.50220985</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.126349250948194</v>
+        <v>0.1275097914959059</v>
       </c>
       <c r="T43">
-        <v>1.570054827222249</v>
+        <v>1.59267592261014</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.346757254262884</v>
+        <v>3.267072557732815</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09414717906762544</v>
+        <v>0.09403755007581642</v>
       </c>
       <c r="C44">
-        <v>294.5138590607324</v>
+        <v>290.529452660508</v>
       </c>
       <c r="D44">
-        <v>447.8358590607324</v>
+        <v>448.5924526605079</v>
       </c>
       <c r="E44">
-        <v>149.722</v>
+        <v>154.463</v>
       </c>
       <c r="F44">
-        <v>199.122</v>
+        <v>203.863</v>
       </c>
       <c r="G44">
         <v>45.8</v>
@@ -4895,28 +4895,28 @@
         <v>41.7</v>
       </c>
       <c r="M44">
-        <v>12.7637202</v>
+        <v>13.0676183</v>
       </c>
       <c r="N44">
-        <v>28.9362798</v>
+        <v>28.6323817</v>
       </c>
       <c r="O44">
-        <v>7.23406995</v>
+        <v>7.158095425000001</v>
       </c>
       <c r="P44">
-        <v>21.70220985</v>
+        <v>21.474286275</v>
       </c>
       <c r="Q44">
-        <v>32.50220985</v>
+        <v>32.27428627500001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1275097914959059</v>
+        <v>0.1287110527645902</v>
       </c>
       <c r="T44">
-        <v>1.59267592261014</v>
+        <v>1.61609074064322</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.267072557732815</v>
+        <v>3.191094126157634</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09403755007581642</v>
+        <v>0.09392792108400741</v>
       </c>
       <c r="C45">
-        <v>290.529452660508</v>
+        <v>286.5476070315804</v>
       </c>
       <c r="D45">
-        <v>448.5924526605079</v>
+        <v>449.3516070315804</v>
       </c>
       <c r="E45">
-        <v>154.463</v>
+        <v>159.204</v>
       </c>
       <c r="F45">
-        <v>203.863</v>
+        <v>208.604</v>
       </c>
       <c r="G45">
         <v>45.8</v>
@@ -4977,28 +4977,28 @@
         <v>41.7</v>
       </c>
       <c r="M45">
-        <v>13.0676183</v>
+        <v>13.3715164</v>
       </c>
       <c r="N45">
-        <v>28.6323817</v>
+        <v>28.32848360000001</v>
       </c>
       <c r="O45">
-        <v>7.158095425000001</v>
+        <v>7.082120900000001</v>
       </c>
       <c r="P45">
-        <v>21.474286275</v>
+        <v>21.24636270000001</v>
       </c>
       <c r="Q45">
-        <v>32.27428627500001</v>
+        <v>32.0463627</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1287110527645902</v>
+        <v>0.1299552162214418</v>
       </c>
       <c r="T45">
-        <v>1.61609074064322</v>
+        <v>1.640341802177482</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.191094126157634</v>
+        <v>3.118569259654052</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09392792108400741</v>
+        <v>0.09381829209219841</v>
       </c>
       <c r="C46">
-        <v>286.5476070315804</v>
+        <v>282.5683351967914</v>
       </c>
       <c r="D46">
-        <v>449.3516070315804</v>
+        <v>450.1133351967914</v>
       </c>
       <c r="E46">
-        <v>159.204</v>
+        <v>163.945</v>
       </c>
       <c r="F46">
-        <v>208.604</v>
+        <v>213.345</v>
       </c>
       <c r="G46">
         <v>45.8</v>
@@ -5059,28 +5059,28 @@
         <v>41.7</v>
       </c>
       <c r="M46">
-        <v>13.3715164</v>
+        <v>13.6754145</v>
       </c>
       <c r="N46">
-        <v>28.32848360000001</v>
+        <v>28.0245855</v>
       </c>
       <c r="O46">
-        <v>7.082120900000001</v>
+        <v>7.006146375</v>
       </c>
       <c r="P46">
-        <v>21.24636270000001</v>
+        <v>21.018439125</v>
       </c>
       <c r="Q46">
-        <v>32.0463627</v>
+        <v>31.818439125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1299552162214418</v>
+        <v>0.1312446219858153</v>
       </c>
       <c r="T46">
-        <v>1.640341802177482</v>
+        <v>1.665474720494808</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.118569259654052</v>
+        <v>3.049267720550628</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09381829209219841</v>
+        <v>0.09639966310038939</v>
       </c>
       <c r="C47">
-        <v>282.5683351967914</v>
+        <v>260.5505608678666</v>
       </c>
       <c r="D47">
-        <v>450.1133351967914</v>
+        <v>432.8365608678666</v>
       </c>
       <c r="E47">
-        <v>163.945</v>
+        <v>168.686</v>
       </c>
       <c r="F47">
-        <v>213.345</v>
+        <v>218.086</v>
       </c>
       <c r="G47">
         <v>45.8</v>
@@ -5141,45 +5141,45 @@
         <v>41.7</v>
       </c>
       <c r="M47">
-        <v>13.6754145</v>
+        <v>15.6803834</v>
       </c>
       <c r="N47">
-        <v>28.0245855</v>
+        <v>26.0196166</v>
       </c>
       <c r="O47">
-        <v>7.006146375</v>
+        <v>6.504904150000001</v>
       </c>
       <c r="P47">
-        <v>21.018439125</v>
+        <v>19.51471245</v>
       </c>
       <c r="Q47">
-        <v>31.818439125</v>
+        <v>30.31471245</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1312446219858153</v>
+        <v>0.1325817835192396</v>
       </c>
       <c r="T47">
-        <v>1.665474720494808</v>
+        <v>1.691538487638702</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.049267720550628</v>
+        <v>2.659373749751553</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09639966310038939</v>
+        <v>0.09634853410858037</v>
       </c>
       <c r="C48">
-        <v>260.5505608678666</v>
+        <v>256.1388760994831</v>
       </c>
       <c r="D48">
-        <v>432.8365608678666</v>
+        <v>433.1658760994831</v>
       </c>
       <c r="E48">
-        <v>168.686</v>
+        <v>173.427</v>
       </c>
       <c r="F48">
-        <v>218.086</v>
+        <v>222.827</v>
       </c>
       <c r="G48">
         <v>45.8</v>
@@ -5223,28 +5223,28 @@
         <v>41.7</v>
       </c>
       <c r="M48">
-        <v>15.6803834</v>
+        <v>16.0212613</v>
       </c>
       <c r="N48">
-        <v>26.0196166</v>
+        <v>25.6787387</v>
       </c>
       <c r="O48">
-        <v>6.504904150000001</v>
+        <v>6.419684675</v>
       </c>
       <c r="P48">
-        <v>19.51471245</v>
+        <v>19.259054025</v>
       </c>
       <c r="Q48">
-        <v>30.31471245</v>
+        <v>30.059054025</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1325817835192396</v>
+        <v>0.1339694039784535</v>
       </c>
       <c r="T48">
-        <v>1.691538487638702</v>
+        <v>1.718585793165384</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.659373749751553</v>
+        <v>2.602791329544073</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09634853410858037</v>
+        <v>0.09629740511677137</v>
       </c>
       <c r="C49">
-        <v>256.1388760994831</v>
+        <v>251.7276928187525</v>
       </c>
       <c r="D49">
-        <v>433.1658760994831</v>
+        <v>433.4956928187525</v>
       </c>
       <c r="E49">
-        <v>173.427</v>
+        <v>178.168</v>
       </c>
       <c r="F49">
-        <v>222.827</v>
+        <v>227.568</v>
       </c>
       <c r="G49">
         <v>45.8</v>
@@ -5305,28 +5305,28 @@
         <v>41.7</v>
       </c>
       <c r="M49">
-        <v>16.0212613</v>
+        <v>16.3621392</v>
       </c>
       <c r="N49">
-        <v>25.6787387</v>
+        <v>25.3378608</v>
       </c>
       <c r="O49">
-        <v>6.419684675</v>
+        <v>6.3344652</v>
       </c>
       <c r="P49">
-        <v>19.259054025</v>
+        <v>19.0033956</v>
       </c>
       <c r="Q49">
-        <v>30.059054025</v>
+        <v>29.8033956</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1339694039784535</v>
+        <v>0.1354103944553295</v>
       </c>
       <c r="T49">
-        <v>1.718585793165384</v>
+        <v>1.746673379673862</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.602791329544073</v>
+        <v>2.548566510178571</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09629740511677137</v>
+        <v>0.09767952612496236</v>
       </c>
       <c r="C50">
-        <v>251.7276928187525</v>
+        <v>238.2442267219519</v>
       </c>
       <c r="D50">
-        <v>433.4956928187525</v>
+        <v>424.7532267219518</v>
       </c>
       <c r="E50">
-        <v>178.168</v>
+        <v>182.909</v>
       </c>
       <c r="F50">
-        <v>227.568</v>
+        <v>232.309</v>
       </c>
       <c r="G50">
         <v>45.8</v>
@@ -5387,45 +5387,45 @@
         <v>41.7</v>
       </c>
       <c r="M50">
-        <v>16.3621392</v>
+        <v>17.6090222</v>
       </c>
       <c r="N50">
-        <v>25.3378608</v>
+        <v>24.0909778</v>
       </c>
       <c r="O50">
-        <v>6.3344652</v>
+        <v>6.022744450000001</v>
       </c>
       <c r="P50">
-        <v>19.0033956</v>
+        <v>18.06823335</v>
       </c>
       <c r="Q50">
-        <v>29.8033956</v>
+        <v>28.86823335</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1354103944553295</v>
+        <v>0.1369078943626713</v>
       </c>
       <c r="T50">
-        <v>1.746673379673862</v>
+        <v>1.775862440163064</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.548566510178571</v>
+        <v>2.368104232386055</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09767952612496236</v>
+        <v>0.09765764713315335</v>
       </c>
       <c r="C51">
-        <v>238.2442267219519</v>
+        <v>233.6388723387632</v>
       </c>
       <c r="D51">
-        <v>424.7532267219518</v>
+        <v>424.8888723387631</v>
       </c>
       <c r="E51">
-        <v>182.909</v>
+        <v>187.65</v>
       </c>
       <c r="F51">
-        <v>232.309</v>
+        <v>237.05</v>
       </c>
       <c r="G51">
         <v>45.8</v>
@@ -5469,28 +5469,28 @@
         <v>41.7</v>
       </c>
       <c r="M51">
-        <v>17.6090222</v>
+        <v>17.96839</v>
       </c>
       <c r="N51">
-        <v>24.0909778</v>
+        <v>23.73161</v>
       </c>
       <c r="O51">
-        <v>6.022744450000001</v>
+        <v>5.932902500000001</v>
       </c>
       <c r="P51">
-        <v>18.06823335</v>
+        <v>17.7987075</v>
       </c>
       <c r="Q51">
-        <v>28.86823335</v>
+        <v>28.5987075</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1369078943626713</v>
+        <v>0.1384652942663067</v>
       </c>
       <c r="T51">
-        <v>1.775862440163064</v>
+        <v>1.806219063071834</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.368104232386055</v>
+        <v>2.320742147738334</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09765764713315335</v>
+        <v>0.09763576814134435</v>
       </c>
       <c r="C52">
-        <v>233.6388723387632</v>
+        <v>229.0336046205368</v>
       </c>
       <c r="D52">
-        <v>424.8888723387631</v>
+        <v>425.0246046205368</v>
       </c>
       <c r="E52">
-        <v>187.65</v>
+        <v>192.391</v>
       </c>
       <c r="F52">
-        <v>237.05</v>
+        <v>241.791</v>
       </c>
       <c r="G52">
         <v>45.8</v>
@@ -5551,28 +5551,28 @@
         <v>41.7</v>
       </c>
       <c r="M52">
-        <v>17.96839</v>
+        <v>18.3277578</v>
       </c>
       <c r="N52">
-        <v>23.73161</v>
+        <v>23.3722422</v>
       </c>
       <c r="O52">
-        <v>5.932902500000001</v>
+        <v>5.843060550000001</v>
       </c>
       <c r="P52">
-        <v>17.7987075</v>
+        <v>17.52918165</v>
       </c>
       <c r="Q52">
-        <v>28.5987075</v>
+        <v>28.32918165</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1384652942663067</v>
+        <v>0.1400862615129476</v>
       </c>
       <c r="T52">
-        <v>1.806219063071834</v>
+        <v>1.837814731813616</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.320742147738334</v>
+        <v>2.275237399743465</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09763576814134435</v>
+        <v>0.09761388914953534</v>
       </c>
       <c r="C53">
-        <v>229.0336046205368</v>
+        <v>224.4284236503559</v>
       </c>
       <c r="D53">
-        <v>425.0246046205368</v>
+        <v>425.1604236503559</v>
       </c>
       <c r="E53">
-        <v>192.391</v>
+        <v>197.132</v>
       </c>
       <c r="F53">
-        <v>241.791</v>
+        <v>246.532</v>
       </c>
       <c r="G53">
         <v>45.8</v>
@@ -5633,28 +5633,28 @@
         <v>41.7</v>
       </c>
       <c r="M53">
-        <v>18.3277578</v>
+        <v>18.6871256</v>
       </c>
       <c r="N53">
-        <v>23.3722422</v>
+        <v>23.0128744</v>
       </c>
       <c r="O53">
-        <v>5.843060550000001</v>
+        <v>5.7532186</v>
       </c>
       <c r="P53">
-        <v>17.52918165</v>
+        <v>17.2596558</v>
       </c>
       <c r="Q53">
-        <v>28.32918165</v>
+        <v>28.0596558</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1400862615129476</v>
+        <v>0.1417747690615319</v>
       </c>
       <c r="T53">
-        <v>1.837814731813616</v>
+        <v>1.870726886752971</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.275237399743465</v>
+        <v>2.231482834363782</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09761388914953534</v>
+        <v>0.09759201015772634</v>
       </c>
       <c r="C54">
-        <v>224.4284236503559</v>
+        <v>219.8233295114093</v>
       </c>
       <c r="D54">
-        <v>425.1604236503559</v>
+        <v>425.2963295114093</v>
       </c>
       <c r="E54">
-        <v>197.132</v>
+        <v>201.873</v>
       </c>
       <c r="F54">
-        <v>246.532</v>
+        <v>251.273</v>
       </c>
       <c r="G54">
         <v>45.8</v>
@@ -5715,28 +5715,28 @@
         <v>41.7</v>
       </c>
       <c r="M54">
-        <v>18.6871256</v>
+        <v>19.0464934</v>
       </c>
       <c r="N54">
-        <v>23.0128744</v>
+        <v>22.6535066</v>
       </c>
       <c r="O54">
-        <v>5.7532186</v>
+        <v>5.66337665</v>
       </c>
       <c r="P54">
-        <v>17.2596558</v>
+        <v>16.99012995</v>
       </c>
       <c r="Q54">
-        <v>28.0596558</v>
+        <v>27.79012995</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1417747690615319</v>
+        <v>0.1435351279951624</v>
       </c>
       <c r="T54">
-        <v>1.870726886752971</v>
+        <v>1.905039558923789</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.231482834363782</v>
+        <v>2.189379384658805</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09759201015772634</v>
+        <v>0.09757013116591731</v>
       </c>
       <c r="C55">
-        <v>219.8233295114093</v>
+        <v>215.2183222869926</v>
       </c>
       <c r="D55">
-        <v>425.2963295114093</v>
+        <v>425.4323222869926</v>
       </c>
       <c r="E55">
-        <v>201.873</v>
+        <v>206.614</v>
       </c>
       <c r="F55">
-        <v>251.273</v>
+        <v>256.014</v>
       </c>
       <c r="G55">
         <v>45.8</v>
@@ -5797,28 +5797,28 @@
         <v>41.7</v>
       </c>
       <c r="M55">
-        <v>19.0464934</v>
+        <v>19.4058612</v>
       </c>
       <c r="N55">
-        <v>22.6535066</v>
+        <v>22.2941388</v>
       </c>
       <c r="O55">
-        <v>5.66337665</v>
+        <v>5.5735347</v>
       </c>
       <c r="P55">
-        <v>16.99012995</v>
+        <v>16.7206041</v>
       </c>
       <c r="Q55">
-        <v>27.79012995</v>
+        <v>27.5206041</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1435351279951624</v>
+        <v>0.1453720242737333</v>
       </c>
       <c r="T55">
-        <v>1.905039558923789</v>
+        <v>1.940844086406381</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.189379384658805</v>
+        <v>2.148835321979939</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09757013116591731</v>
+        <v>0.09754825217410831</v>
       </c>
       <c r="C56">
-        <v>215.2183222869926</v>
+        <v>210.6134020605078</v>
       </c>
       <c r="D56">
-        <v>425.4323222869926</v>
+        <v>425.5684020605078</v>
       </c>
       <c r="E56">
-        <v>206.614</v>
+        <v>211.355</v>
       </c>
       <c r="F56">
-        <v>256.014</v>
+        <v>260.755</v>
       </c>
       <c r="G56">
         <v>45.8</v>
@@ -5879,28 +5879,28 @@
         <v>41.7</v>
       </c>
       <c r="M56">
-        <v>19.4058612</v>
+        <v>19.765229</v>
       </c>
       <c r="N56">
-        <v>22.2941388</v>
+        <v>21.934771</v>
       </c>
       <c r="O56">
-        <v>5.5735347</v>
+        <v>5.48369275</v>
       </c>
       <c r="P56">
-        <v>16.7206041</v>
+        <v>16.45107825</v>
       </c>
       <c r="Q56">
-        <v>27.5206041</v>
+        <v>27.25107825</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1453720242737333</v>
+        <v>0.1472905603869074</v>
       </c>
       <c r="T56">
-        <v>1.940844086406381</v>
+        <v>1.978239926221533</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.148835321979939</v>
+        <v>2.109765588853031</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09754825217410831</v>
+        <v>0.09752637318229929</v>
       </c>
       <c r="C57">
-        <v>210.6134020605078</v>
+        <v>206.0085689154637</v>
       </c>
       <c r="D57">
-        <v>425.5684020605078</v>
+        <v>425.7045689154637</v>
       </c>
       <c r="E57">
-        <v>211.355</v>
+        <v>216.096</v>
       </c>
       <c r="F57">
-        <v>260.755</v>
+        <v>265.496</v>
       </c>
       <c r="G57">
         <v>45.8</v>
@@ -5961,28 +5961,28 @@
         <v>41.7</v>
       </c>
       <c r="M57">
-        <v>19.765229</v>
+        <v>20.1245968</v>
       </c>
       <c r="N57">
-        <v>21.934771</v>
+        <v>21.5754032</v>
       </c>
       <c r="O57">
-        <v>5.48369275</v>
+        <v>5.393850800000001</v>
       </c>
       <c r="P57">
-        <v>16.45107825</v>
+        <v>16.1815524</v>
       </c>
       <c r="Q57">
-        <v>27.25107825</v>
+        <v>26.9815524</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1472905603869074</v>
+        <v>0.1492963026870438</v>
       </c>
       <c r="T57">
-        <v>1.978239926221533</v>
+        <v>2.017335576937374</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.109765588853031</v>
+        <v>2.072091203337799</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09752637318229929</v>
+        <v>0.09750449419049027</v>
       </c>
       <c r="C58">
-        <v>206.0085689154637</v>
+        <v>201.403822935476</v>
       </c>
       <c r="D58">
-        <v>425.7045689154637</v>
+        <v>425.840822935476</v>
       </c>
       <c r="E58">
-        <v>216.096</v>
+        <v>220.837</v>
       </c>
       <c r="F58">
-        <v>265.496</v>
+        <v>270.237</v>
       </c>
       <c r="G58">
         <v>45.8</v>
@@ -6043,28 +6043,28 @@
         <v>41.7</v>
       </c>
       <c r="M58">
-        <v>20.1245968</v>
+        <v>20.4839646</v>
       </c>
       <c r="N58">
-        <v>21.5754032</v>
+        <v>21.2160354</v>
       </c>
       <c r="O58">
-        <v>5.393850800000001</v>
+        <v>5.30400885</v>
       </c>
       <c r="P58">
-        <v>16.1815524</v>
+        <v>15.91202655</v>
       </c>
       <c r="Q58">
-        <v>26.9815524</v>
+        <v>26.71202655</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1492963026870438</v>
+        <v>0.1513953353267216</v>
       </c>
       <c r="T58">
-        <v>2.017335576937374</v>
+        <v>2.05824963001209</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.072091203337799</v>
+        <v>2.035738726086258</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09750449419049027</v>
+        <v>0.09748261519868129</v>
       </c>
       <c r="C59">
-        <v>201.403822935476</v>
+        <v>196.7991642042673</v>
       </c>
       <c r="D59">
-        <v>425.840822935476</v>
+        <v>425.9771642042673</v>
       </c>
       <c r="E59">
-        <v>220.837</v>
+        <v>225.578</v>
       </c>
       <c r="F59">
-        <v>270.237</v>
+        <v>274.978</v>
       </c>
       <c r="G59">
         <v>45.8</v>
@@ -6125,28 +6125,28 @@
         <v>41.7</v>
       </c>
       <c r="M59">
-        <v>20.4839646</v>
+        <v>20.8433324</v>
       </c>
       <c r="N59">
-        <v>21.2160354</v>
+        <v>20.8566676</v>
       </c>
       <c r="O59">
-        <v>5.30400885</v>
+        <v>5.2141669</v>
       </c>
       <c r="P59">
-        <v>15.91202655</v>
+        <v>15.6425007</v>
       </c>
       <c r="Q59">
-        <v>26.71202655</v>
+        <v>26.4425007</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1513953353267216</v>
+        <v>0.1535943219016221</v>
       </c>
       <c r="T59">
-        <v>2.05824963001209</v>
+        <v>2.101111971328461</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.035738726086258</v>
+        <v>2.000639782533046</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09748261519868127</v>
+        <v>0.1037442362068723</v>
       </c>
       <c r="C60">
-        <v>196.7991642042675</v>
+        <v>156.3020584138882</v>
       </c>
       <c r="D60">
-        <v>425.9771642042674</v>
+        <v>390.2210584138882</v>
       </c>
       <c r="E60">
-        <v>225.5779999999999</v>
+        <v>230.3189999999999</v>
       </c>
       <c r="F60">
-        <v>274.978</v>
+        <v>279.7189999999999</v>
       </c>
       <c r="G60">
         <v>45.8</v>
@@ -6207,45 +6207,45 @@
         <v>41.7</v>
       </c>
       <c r="M60">
-        <v>20.8433324</v>
+        <v>25.17470999999999</v>
       </c>
       <c r="N60">
-        <v>20.85666760000001</v>
+        <v>16.52529000000001</v>
       </c>
       <c r="O60">
-        <v>5.214166900000001</v>
+        <v>4.131322500000002</v>
       </c>
       <c r="P60">
-        <v>15.6425007</v>
+        <v>12.39396750000001</v>
       </c>
       <c r="Q60">
-        <v>26.4425007</v>
+        <v>23.19396750000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1535943219016221</v>
+        <v>0.1559005761143226</v>
       </c>
       <c r="T60">
-        <v>2.10111197132846</v>
+        <v>2.146065158562702</v>
       </c>
       <c r="U60">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.000639782533047</v>
+        <v>1.656424244807587</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1037442362068723</v>
+        <v>0.1038288572150632</v>
       </c>
       <c r="C61">
-        <v>156.3020584138882</v>
+        <v>151.118904327275</v>
       </c>
       <c r="D61">
-        <v>390.2210584138882</v>
+        <v>389.778904327275</v>
       </c>
       <c r="E61">
-        <v>230.3189999999999</v>
+        <v>235.06</v>
       </c>
       <c r="F61">
-        <v>279.7189999999999</v>
+        <v>284.46</v>
       </c>
       <c r="G61">
         <v>45.8</v>
@@ -6289,28 +6289,28 @@
         <v>41.7</v>
       </c>
       <c r="M61">
-        <v>25.17470999999999</v>
+        <v>25.6014</v>
       </c>
       <c r="N61">
-        <v>16.52529000000001</v>
+        <v>16.0986</v>
       </c>
       <c r="O61">
-        <v>4.131322500000002</v>
+        <v>4.024650000000001</v>
       </c>
       <c r="P61">
-        <v>12.39396750000001</v>
+        <v>12.07395</v>
       </c>
       <c r="Q61">
-        <v>23.19396750000001</v>
+        <v>22.87395</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1559005761143226</v>
+        <v>0.1583221430376581</v>
       </c>
       <c r="T61">
-        <v>2.146065158562702</v>
+        <v>2.193266005158656</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.656424244807587</v>
+        <v>1.628817174060794</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1038288572150632</v>
+        <v>0.1039134782232543</v>
       </c>
       <c r="C62">
-        <v>151.118904327275</v>
+        <v>145.9367511039629</v>
       </c>
       <c r="D62">
-        <v>389.778904327275</v>
+        <v>389.3377511039629</v>
       </c>
       <c r="E62">
-        <v>235.06</v>
+        <v>239.801</v>
       </c>
       <c r="F62">
-        <v>284.46</v>
+        <v>289.201</v>
       </c>
       <c r="G62">
         <v>45.8</v>
@@ -6371,28 +6371,28 @@
         <v>41.7</v>
       </c>
       <c r="M62">
-        <v>25.6014</v>
+        <v>26.02809</v>
       </c>
       <c r="N62">
-        <v>16.0986</v>
+        <v>15.67191000000001</v>
       </c>
       <c r="O62">
-        <v>4.024650000000001</v>
+        <v>3.917977500000002</v>
       </c>
       <c r="P62">
-        <v>12.07395</v>
+        <v>11.7539325</v>
       </c>
       <c r="Q62">
-        <v>22.87395</v>
+        <v>22.55393250000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1583221430376581</v>
+        <v>0.1608678928801391</v>
       </c>
       <c r="T62">
-        <v>2.193266005158656</v>
+        <v>2.2428874079903</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.628817174060794</v>
+        <v>1.602115253174552</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1039134782232543</v>
+        <v>0.1039980992314452</v>
       </c>
       <c r="C63">
-        <v>145.9367511039629</v>
+        <v>140.7555953494519</v>
       </c>
       <c r="D63">
-        <v>389.3377511039629</v>
+        <v>388.8975953494519</v>
       </c>
       <c r="E63">
-        <v>239.801</v>
+        <v>244.5419999999999</v>
       </c>
       <c r="F63">
-        <v>289.201</v>
+        <v>293.942</v>
       </c>
       <c r="G63">
         <v>45.8</v>
@@ -6453,28 +6453,28 @@
         <v>41.7</v>
       </c>
       <c r="M63">
-        <v>26.02809</v>
+        <v>26.45478</v>
       </c>
       <c r="N63">
-        <v>15.67191000000001</v>
+        <v>15.24522000000001</v>
       </c>
       <c r="O63">
-        <v>3.917977500000002</v>
+        <v>3.811305000000002</v>
       </c>
       <c r="P63">
-        <v>11.7539325</v>
+        <v>11.43391500000001</v>
       </c>
       <c r="Q63">
-        <v>22.55393250000001</v>
+        <v>22.23391500000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1608678928801391</v>
+        <v>0.1635476295564348</v>
       </c>
       <c r="T63">
-        <v>2.2428874079903</v>
+        <v>2.295120463602557</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.602115253174552</v>
+        <v>1.576274684574962</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1039980992314452</v>
+        <v>0.1040827202396362</v>
       </c>
       <c r="C64">
-        <v>140.7555953494519</v>
+        <v>135.5754336845741</v>
       </c>
       <c r="D64">
-        <v>388.8975953494519</v>
+        <v>388.4584336845741</v>
       </c>
       <c r="E64">
-        <v>244.5419999999999</v>
+        <v>249.283</v>
       </c>
       <c r="F64">
-        <v>293.942</v>
+        <v>298.683</v>
       </c>
       <c r="G64">
         <v>45.8</v>
@@ -6535,28 +6535,28 @@
         <v>41.7</v>
       </c>
       <c r="M64">
-        <v>26.45478</v>
+        <v>26.88147</v>
       </c>
       <c r="N64">
-        <v>15.24522000000001</v>
+        <v>14.81853000000001</v>
       </c>
       <c r="O64">
-        <v>3.811305000000002</v>
+        <v>3.704632500000002</v>
       </c>
       <c r="P64">
-        <v>11.43391500000001</v>
+        <v>11.1138975</v>
       </c>
       <c r="Q64">
-        <v>22.23391500000001</v>
+        <v>21.9138975</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1635476295564348</v>
+        <v>0.1663722168638817</v>
       </c>
       <c r="T64">
-        <v>2.295120463602557</v>
+        <v>2.350176927626287</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.576274684574962</v>
+        <v>1.55125445148647</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1040827202396362</v>
+        <v>0.1041673412478272</v>
       </c>
       <c r="C65">
-        <v>135.5754336845741</v>
+        <v>130.3962627454083</v>
       </c>
       <c r="D65">
-        <v>388.4584336845741</v>
+        <v>388.0202627454082</v>
       </c>
       <c r="E65">
-        <v>249.283</v>
+        <v>254.024</v>
       </c>
       <c r="F65">
-        <v>298.683</v>
+        <v>303.424</v>
       </c>
       <c r="G65">
         <v>45.8</v>
@@ -6617,28 +6617,28 @@
         <v>41.7</v>
       </c>
       <c r="M65">
-        <v>26.88147</v>
+        <v>27.30816</v>
       </c>
       <c r="N65">
-        <v>14.81853000000001</v>
+        <v>14.39184000000001</v>
       </c>
       <c r="O65">
-        <v>3.704632500000002</v>
+        <v>3.597960000000001</v>
       </c>
       <c r="P65">
-        <v>11.1138975</v>
+        <v>10.79388000000001</v>
       </c>
       <c r="Q65">
-        <v>21.9138975</v>
+        <v>21.59388000000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1663722168638817</v>
+        <v>0.169353725688409</v>
       </c>
       <c r="T65">
-        <v>2.350176927626287</v>
+        <v>2.40829208409578</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.55125445148647</v>
+        <v>1.527016100681994</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1041673412478272</v>
+        <v>0.1042519622560182</v>
       </c>
       <c r="C66">
-        <v>130.3962627454083</v>
+        <v>125.2180791831937</v>
       </c>
       <c r="D66">
-        <v>388.0202627454082</v>
+        <v>387.5830791831937</v>
       </c>
       <c r="E66">
-        <v>254.024</v>
+        <v>258.765</v>
       </c>
       <c r="F66">
-        <v>303.424</v>
+        <v>308.165</v>
       </c>
       <c r="G66">
         <v>45.8</v>
@@ -6699,28 +6699,28 @@
         <v>41.7</v>
       </c>
       <c r="M66">
-        <v>27.30816</v>
+        <v>27.73484999999999</v>
       </c>
       <c r="N66">
-        <v>14.39184000000001</v>
+        <v>13.96515000000001</v>
       </c>
       <c r="O66">
-        <v>3.597960000000001</v>
+        <v>3.491287500000002</v>
       </c>
       <c r="P66">
-        <v>10.79388000000001</v>
+        <v>10.47386250000001</v>
       </c>
       <c r="Q66">
-        <v>21.59388000000001</v>
+        <v>21.27386250000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.169353725688409</v>
+        <v>0.1725056064457663</v>
       </c>
       <c r="T66">
-        <v>2.40829208409578</v>
+        <v>2.469728106649244</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.527016100681994</v>
+        <v>1.503523545286887</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1042519622560182</v>
+        <v>0.135490995753523</v>
       </c>
       <c r="C67">
-        <v>125.2180791831937</v>
+        <v>6.62280963975536</v>
       </c>
       <c r="D67">
-        <v>387.5830791831937</v>
+        <v>273.7288096397554</v>
       </c>
       <c r="E67">
-        <v>258.765</v>
+        <v>263.506</v>
       </c>
       <c r="F67">
-        <v>308.165</v>
+        <v>312.906</v>
       </c>
       <c r="G67">
         <v>45.8</v>
@@ -6781,45 +6781,45 @@
         <v>41.7</v>
       </c>
       <c r="M67">
-        <v>27.73484999999999</v>
+        <v>45.93460080000001</v>
       </c>
       <c r="N67">
-        <v>13.96515000000001</v>
+        <v>-4.234600800000003</v>
       </c>
       <c r="O67">
-        <v>3.491287500000002</v>
+        <v>-1.058650200000001</v>
       </c>
       <c r="P67">
-        <v>10.47386250000001</v>
+        <v>-3.175950600000002</v>
       </c>
       <c r="Q67">
-        <v>21.27386250000001</v>
+        <v>7.624049399999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1725056064457663</v>
+        <v>0.1782118458921874</v>
       </c>
       <c r="T67">
-        <v>2.469728106649244</v>
+        <v>2.580953334477886</v>
       </c>
       <c r="U67">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.25</v>
+        <v>0.2269530989371306</v>
       </c>
       <c r="W67">
-        <v>0.0675</v>
+        <v>0.1134832850760292</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.503523545286887</v>
+        <v>0.9078123957485225</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.135490995753523</v>
+        <v>0.136500995753523</v>
       </c>
       <c r="C68">
-        <v>6.62280963975536</v>
+        <v>-0.6934651008764945</v>
       </c>
       <c r="D68">
-        <v>273.7288096397554</v>
+        <v>271.1535348991235</v>
       </c>
       <c r="E68">
-        <v>263.506</v>
+        <v>268.247</v>
       </c>
       <c r="F68">
-        <v>312.906</v>
+        <v>317.647</v>
       </c>
       <c r="G68">
         <v>45.8</v>
@@ -6863,37 +6863,37 @@
         <v>41.7</v>
       </c>
       <c r="M68">
-        <v>45.93460080000001</v>
+        <v>46.6305796</v>
       </c>
       <c r="N68">
-        <v>-4.234600800000003</v>
+        <v>-4.930579600000002</v>
       </c>
       <c r="O68">
-        <v>-1.058650200000001</v>
+        <v>-1.2326449</v>
       </c>
       <c r="P68">
-        <v>-3.175950600000002</v>
+        <v>-3.697934700000001</v>
       </c>
       <c r="Q68">
-        <v>7.624049399999999</v>
+        <v>7.1020653</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1782118458921874</v>
+        <v>0.1822243260707385</v>
       </c>
       <c r="T68">
-        <v>2.580953334477886</v>
+        <v>2.659164041583276</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2269530989371306</v>
+        <v>0.2235657392515018</v>
       </c>
       <c r="W68">
-        <v>0.1134832850760292</v>
+        <v>0.1139805494778795</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9078123957485225</v>
+        <v>0.8942629570060072</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.136500995753523</v>
+        <v>0.137510995753523</v>
       </c>
       <c r="C69">
-        <v>-0.6934651008764945</v>
+        <v>-7.961734470870397</v>
       </c>
       <c r="D69">
-        <v>271.1535348991235</v>
+        <v>268.6262655291296</v>
       </c>
       <c r="E69">
-        <v>268.247</v>
+        <v>272.988</v>
       </c>
       <c r="F69">
-        <v>317.647</v>
+        <v>322.388</v>
       </c>
       <c r="G69">
         <v>45.8</v>
@@ -6945,37 +6945,37 @@
         <v>41.7</v>
       </c>
       <c r="M69">
-        <v>46.6305796</v>
+        <v>47.3265584</v>
       </c>
       <c r="N69">
-        <v>-4.930579600000002</v>
+        <v>-5.6265584</v>
       </c>
       <c r="O69">
-        <v>-1.2326449</v>
+        <v>-1.4066396</v>
       </c>
       <c r="P69">
-        <v>-3.697934700000001</v>
+        <v>-4.2199188</v>
       </c>
       <c r="Q69">
-        <v>7.1020653</v>
+        <v>6.5800812</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1822243260707385</v>
+        <v>0.1864875862604491</v>
       </c>
       <c r="T69">
-        <v>2.659164041583276</v>
+        <v>2.742262917882754</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2235657392515018</v>
+        <v>0.2202780077919209</v>
       </c>
       <c r="W69">
-        <v>0.1139805494778795</v>
+        <v>0.114463188456146</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8942629570060072</v>
+        <v>0.8811120311676837</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.137510995753523</v>
+        <v>0.138520995753523</v>
       </c>
       <c r="C70">
-        <v>-7.961734470870397</v>
+        <v>-15.18332836805905</v>
       </c>
       <c r="D70">
-        <v>268.6262655291296</v>
+        <v>266.145671631941</v>
       </c>
       <c r="E70">
-        <v>272.988</v>
+        <v>277.729</v>
       </c>
       <c r="F70">
-        <v>322.388</v>
+        <v>327.129</v>
       </c>
       <c r="G70">
         <v>45.8</v>
@@ -7027,37 +7027,37 @@
         <v>41.7</v>
       </c>
       <c r="M70">
-        <v>47.3265584</v>
+        <v>48.02253720000001</v>
       </c>
       <c r="N70">
-        <v>-5.6265584</v>
+        <v>-6.322537200000006</v>
       </c>
       <c r="O70">
-        <v>-1.4066396</v>
+        <v>-1.580634300000002</v>
       </c>
       <c r="P70">
-        <v>-4.2199188</v>
+        <v>-4.741902900000005</v>
       </c>
       <c r="Q70">
-        <v>6.5800812</v>
+        <v>6.058097099999996</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1864875862604491</v>
+        <v>0.1910258954946571</v>
       </c>
       <c r="T70">
-        <v>2.742262917882754</v>
+        <v>2.830723012008004</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2202780077919209</v>
+        <v>0.2170855728963858</v>
       </c>
       <c r="W70">
-        <v>0.114463188456146</v>
+        <v>0.1149318378988106</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8811120311676837</v>
+        <v>0.8683422915855432</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.138520995753523</v>
+        <v>0.139530995753523</v>
       </c>
       <c r="C71">
-        <v>-15.18332836805905</v>
+        <v>-22.35952801667867</v>
       </c>
       <c r="D71">
-        <v>266.145671631941</v>
+        <v>263.7104719833213</v>
       </c>
       <c r="E71">
-        <v>277.729</v>
+        <v>282.47</v>
       </c>
       <c r="F71">
-        <v>327.129</v>
+        <v>331.87</v>
       </c>
       <c r="G71">
         <v>45.8</v>
@@ -7109,37 +7109,37 @@
         <v>41.7</v>
       </c>
       <c r="M71">
-        <v>48.02253720000001</v>
+        <v>48.71851600000001</v>
       </c>
       <c r="N71">
-        <v>-6.322537200000006</v>
+        <v>-7.018516000000005</v>
       </c>
       <c r="O71">
-        <v>-1.580634300000002</v>
+        <v>-1.754629000000001</v>
       </c>
       <c r="P71">
-        <v>-4.741902900000005</v>
+        <v>-5.263887000000004</v>
       </c>
       <c r="Q71">
-        <v>6.058097099999996</v>
+        <v>5.536112999999997</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1910258954946571</v>
+        <v>0.1958667586778124</v>
       </c>
       <c r="T71">
-        <v>2.830723012008004</v>
+        <v>2.925080445741604</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2170855728963858</v>
+        <v>0.2139843504264374</v>
       </c>
       <c r="W71">
-        <v>0.1149318378988106</v>
+        <v>0.115387097357399</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8683422915855432</v>
+        <v>0.8559374017057497</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.139530995753523</v>
+        <v>0.140540995753523</v>
       </c>
       <c r="C72">
-        <v>-22.35952801667867</v>
+        <v>-29.49156817396607</v>
       </c>
       <c r="D72">
-        <v>263.7104719833213</v>
+        <v>261.3194318260339</v>
       </c>
       <c r="E72">
-        <v>282.47</v>
+        <v>287.211</v>
       </c>
       <c r="F72">
-        <v>331.87</v>
+        <v>336.611</v>
       </c>
       <c r="G72">
         <v>45.8</v>
@@ -7191,37 +7191,37 @@
         <v>41.7</v>
       </c>
       <c r="M72">
-        <v>48.71851600000001</v>
+        <v>49.4144948</v>
       </c>
       <c r="N72">
-        <v>-7.018516000000005</v>
+        <v>-7.714494799999997</v>
       </c>
       <c r="O72">
-        <v>-1.754629000000001</v>
+        <v>-1.928623699999999</v>
       </c>
       <c r="P72">
-        <v>-5.263887000000004</v>
+        <v>-5.785871099999998</v>
       </c>
       <c r="Q72">
-        <v>5.536112999999997</v>
+        <v>5.014128900000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1958667586778124</v>
+        <v>0.2010414744942887</v>
       </c>
       <c r="T72">
-        <v>2.925080445741604</v>
+        <v>3.025945288698212</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2139843504264374</v>
+        <v>0.2109704863359243</v>
       </c>
       <c r="W72">
-        <v>0.115387097357399</v>
+        <v>0.1158295326058863</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8559374017057497</v>
+        <v>0.8438819453436971</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.140540995753523</v>
+        <v>0.141550995753523</v>
       </c>
       <c r="C73">
-        <v>-29.4915681739659</v>
+        <v>-36.58063921779183</v>
       </c>
       <c r="D73">
-        <v>261.319431826034</v>
+        <v>258.9713607822081</v>
       </c>
       <c r="E73">
-        <v>287.211</v>
+        <v>291.952</v>
       </c>
       <c r="F73">
-        <v>336.6109999999999</v>
+        <v>341.352</v>
       </c>
       <c r="G73">
         <v>45.8</v>
@@ -7273,37 +7273,37 @@
         <v>41.7</v>
       </c>
       <c r="M73">
-        <v>49.41449479999999</v>
+        <v>50.1104736</v>
       </c>
       <c r="N73">
-        <v>-7.71449479999999</v>
+        <v>-8.410473599999996</v>
       </c>
       <c r="O73">
-        <v>-1.928623699999997</v>
+        <v>-2.102618399999999</v>
       </c>
       <c r="P73">
-        <v>-5.785871099999992</v>
+        <v>-6.307855199999997</v>
       </c>
       <c r="Q73">
-        <v>5.014128900000008</v>
+        <v>4.492144800000004</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2010414744942886</v>
+        <v>0.2065858128690846</v>
       </c>
       <c r="T73">
-        <v>3.02594528869821</v>
+        <v>3.134014763294575</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2109704863359243</v>
+        <v>0.2080403406923698</v>
       </c>
       <c r="W73">
-        <v>0.1158295326058863</v>
+        <v>0.1162596779863601</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8438819453436972</v>
+        <v>0.8321613627694791</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.141550995753523</v>
+        <v>0.142560995753523</v>
       </c>
       <c r="C74">
-        <v>-36.58063921779183</v>
+        <v>-43.62788912274493</v>
       </c>
       <c r="D74">
-        <v>258.9713607822081</v>
+        <v>256.665110877255</v>
       </c>
       <c r="E74">
-        <v>291.952</v>
+        <v>296.693</v>
       </c>
       <c r="F74">
-        <v>341.352</v>
+        <v>346.093</v>
       </c>
       <c r="G74">
         <v>45.8</v>
@@ -7355,37 +7355,37 @@
         <v>41.7</v>
       </c>
       <c r="M74">
-        <v>50.1104736</v>
+        <v>50.8064524</v>
       </c>
       <c r="N74">
-        <v>-8.410473599999996</v>
+        <v>-9.106452399999995</v>
       </c>
       <c r="O74">
-        <v>-2.102618399999999</v>
+        <v>-2.276613099999999</v>
       </c>
       <c r="P74">
-        <v>-6.307855199999997</v>
+        <v>-6.829839299999996</v>
       </c>
       <c r="Q74">
-        <v>4.492144800000004</v>
+        <v>3.970160700000005</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2065858128690846</v>
+        <v>0.212540842975347</v>
       </c>
       <c r="T74">
-        <v>3.134014763294575</v>
+        <v>3.250089384157337</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2080403406923698</v>
+        <v>0.2051904730116524</v>
       </c>
       <c r="W74">
-        <v>0.1162596779863601</v>
+        <v>0.1166780385618894</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8321613627694791</v>
+        <v>0.8207618920466095</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.142560995753523</v>
+        <v>0.143570995753523</v>
       </c>
       <c r="C75">
-        <v>-43.62788912274493</v>
+        <v>-50.63442533156393</v>
       </c>
       <c r="D75">
-        <v>256.665110877255</v>
+        <v>254.399574668436</v>
       </c>
       <c r="E75">
-        <v>296.693</v>
+        <v>301.434</v>
       </c>
       <c r="F75">
-        <v>346.093</v>
+        <v>350.8339999999999</v>
       </c>
       <c r="G75">
         <v>45.8</v>
@@ -7437,37 +7437,37 @@
         <v>41.7</v>
       </c>
       <c r="M75">
-        <v>50.8064524</v>
+        <v>51.5024312</v>
       </c>
       <c r="N75">
-        <v>-9.106452399999995</v>
+        <v>-9.802431199999994</v>
       </c>
       <c r="O75">
-        <v>-2.276613099999999</v>
+        <v>-2.450607799999998</v>
       </c>
       <c r="P75">
-        <v>-6.829839299999996</v>
+        <v>-7.351823399999995</v>
       </c>
       <c r="Q75">
-        <v>3.970160700000005</v>
+        <v>3.448176600000005</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.212540842975347</v>
+        <v>0.2189539523205527</v>
       </c>
       <c r="T75">
-        <v>3.250089384157337</v>
+        <v>3.375092822009543</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2051904730116524</v>
+        <v>0.2024176287817652</v>
       </c>
       <c r="W75">
-        <v>0.1166780385618894</v>
+        <v>0.1170850920948369</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8207618920466095</v>
+        <v>0.8096705151270608</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.143570995753523</v>
+        <v>0.1872139874492105</v>
       </c>
       <c r="C76">
-        <v>-50.63442533156393</v>
+        <v>-125.616257738584</v>
       </c>
       <c r="D76">
-        <v>254.399574668436</v>
+        <v>184.1587422614161</v>
       </c>
       <c r="E76">
-        <v>301.434</v>
+        <v>306.175</v>
       </c>
       <c r="F76">
-        <v>350.8339999999999</v>
+        <v>355.575</v>
       </c>
       <c r="G76">
         <v>45.8</v>
@@ -7519,45 +7519,45 @@
         <v>41.7</v>
       </c>
       <c r="M76">
-        <v>51.5024312</v>
+        <v>71.39946</v>
       </c>
       <c r="N76">
-        <v>-9.802431199999994</v>
+        <v>-29.69946</v>
       </c>
       <c r="O76">
-        <v>-2.450607799999998</v>
+        <v>-7.424865</v>
       </c>
       <c r="P76">
-        <v>-7.351823399999995</v>
+        <v>-22.274595</v>
       </c>
       <c r="Q76">
-        <v>3.448176600000005</v>
+        <v>-11.474595</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2189539523205527</v>
+        <v>0.2344120771961248</v>
       </c>
       <c r="T76">
-        <v>3.375092822009543</v>
+        <v>3.676400448027143</v>
       </c>
       <c r="U76">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.2024176287817652</v>
+        <v>0.1460095076349317</v>
       </c>
       <c r="W76">
-        <v>0.1170850920948369</v>
+        <v>0.1714812908669057</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.8096705151270608</v>
+        <v>0.5840380305397268</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1872139874492105</v>
+        <v>0.1887639874492105</v>
       </c>
       <c r="C77">
-        <v>-125.616257738584</v>
+        <v>-132.1455762033577</v>
       </c>
       <c r="D77">
-        <v>184.1587422614161</v>
+        <v>182.3704237966423</v>
       </c>
       <c r="E77">
-        <v>306.175</v>
+        <v>310.916</v>
       </c>
       <c r="F77">
-        <v>355.575</v>
+        <v>360.316</v>
       </c>
       <c r="G77">
         <v>45.8</v>
@@ -7601,37 +7601,37 @@
         <v>41.7</v>
       </c>
       <c r="M77">
-        <v>71.39946</v>
+        <v>72.3514528</v>
       </c>
       <c r="N77">
-        <v>-29.69946</v>
+        <v>-30.6514528</v>
       </c>
       <c r="O77">
-        <v>-7.424865</v>
+        <v>-7.6628632</v>
       </c>
       <c r="P77">
-        <v>-22.274595</v>
+        <v>-22.9885896</v>
       </c>
       <c r="Q77">
-        <v>-11.474595</v>
+        <v>-12.1885896</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2344120771961248</v>
+        <v>0.2422709137459633</v>
       </c>
       <c r="T77">
-        <v>3.676400448027143</v>
+        <v>3.829583800028273</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1460095076349317</v>
+        <v>0.1440883299028931</v>
       </c>
       <c r="W77">
-        <v>0.1714812908669057</v>
+        <v>0.1718670633554991</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5840380305397268</v>
+        <v>0.5763533196115724</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1887639874492105</v>
+        <v>0.1903139874492105</v>
       </c>
       <c r="C78">
-        <v>-132.1455762033577</v>
+        <v>-138.640496889334</v>
       </c>
       <c r="D78">
-        <v>182.3704237966423</v>
+        <v>180.6165031106659</v>
       </c>
       <c r="E78">
-        <v>310.916</v>
+        <v>315.657</v>
       </c>
       <c r="F78">
-        <v>360.316</v>
+        <v>365.057</v>
       </c>
       <c r="G78">
         <v>45.8</v>
@@ -7683,37 +7683,37 @@
         <v>41.7</v>
       </c>
       <c r="M78">
-        <v>72.3514528</v>
+        <v>73.30344559999999</v>
       </c>
       <c r="N78">
-        <v>-30.6514528</v>
+        <v>-31.60344559999999</v>
       </c>
       <c r="O78">
-        <v>-7.6628632</v>
+        <v>-7.900861399999997</v>
       </c>
       <c r="P78">
-        <v>-22.9885896</v>
+        <v>-23.70258419999999</v>
       </c>
       <c r="Q78">
-        <v>-12.1885896</v>
+        <v>-12.90258419999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2422709137459633</v>
+        <v>0.2508131273870921</v>
       </c>
       <c r="T78">
-        <v>3.829583800028273</v>
+        <v>3.996087443507764</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1440883299028931</v>
+        <v>0.1422170528911673</v>
       </c>
       <c r="W78">
-        <v>0.1718670633554991</v>
+        <v>0.1722428157794536</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5763533196115724</v>
+        <v>0.568868211564669</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1903139874492105</v>
+        <v>0.1918639874492105</v>
       </c>
       <c r="C79">
-        <v>-138.640496889334</v>
+        <v>-145.1020027894348</v>
       </c>
       <c r="D79">
-        <v>180.6165031106659</v>
+        <v>178.8959972105652</v>
       </c>
       <c r="E79">
-        <v>315.657</v>
+        <v>320.398</v>
       </c>
       <c r="F79">
-        <v>365.057</v>
+        <v>369.798</v>
       </c>
       <c r="G79">
         <v>45.8</v>
@@ -7765,37 +7765,37 @@
         <v>41.7</v>
       </c>
       <c r="M79">
-        <v>73.30344559999999</v>
+        <v>74.2554384</v>
       </c>
       <c r="N79">
-        <v>-31.60344559999999</v>
+        <v>-32.5554384</v>
       </c>
       <c r="O79">
-        <v>-7.900861399999997</v>
+        <v>-8.1388596</v>
       </c>
       <c r="P79">
-        <v>-23.70258419999999</v>
+        <v>-24.4165788</v>
       </c>
       <c r="Q79">
-        <v>-12.90258419999999</v>
+        <v>-13.6165788</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2508131273870921</v>
+        <v>0.2601319059046872</v>
       </c>
       <c r="T79">
-        <v>3.996087443507764</v>
+        <v>4.177727781849025</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1422170528911673</v>
+        <v>0.1403937573412805</v>
       </c>
       <c r="W79">
-        <v>0.1722428157794536</v>
+        <v>0.1726089335258709</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.568868211564669</v>
+        <v>0.5615750293651219</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1918639874492105</v>
+        <v>0.1934139874492105</v>
       </c>
       <c r="C80">
-        <v>-145.1020027894348</v>
+        <v>-151.5310397950598</v>
       </c>
       <c r="D80">
-        <v>178.8959972105652</v>
+        <v>177.2079602049402</v>
       </c>
       <c r="E80">
-        <v>320.398</v>
+        <v>325.139</v>
       </c>
       <c r="F80">
-        <v>369.798</v>
+        <v>374.539</v>
       </c>
       <c r="G80">
         <v>45.8</v>
@@ -7847,37 +7847,37 @@
         <v>41.7</v>
       </c>
       <c r="M80">
-        <v>74.2554384</v>
+        <v>75.2074312</v>
       </c>
       <c r="N80">
-        <v>-32.5554384</v>
+        <v>-33.5074312</v>
       </c>
       <c r="O80">
-        <v>-8.1388596</v>
+        <v>-8.3768578</v>
       </c>
       <c r="P80">
-        <v>-24.4165788</v>
+        <v>-25.1305734</v>
       </c>
       <c r="Q80">
-        <v>-13.6165788</v>
+        <v>-14.3305734</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2601319059046872</v>
+        <v>0.2703381871382438</v>
       </c>
       <c r="T80">
-        <v>4.177727781849025</v>
+        <v>4.376667200032313</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1403937573412805</v>
+        <v>0.1386166211724035</v>
       </c>
       <c r="W80">
-        <v>0.1726089335258709</v>
+        <v>0.1729657824685814</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5615750293651219</v>
+        <v>0.5544664846896141</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1934139874492105</v>
+        <v>0.1949639874492105</v>
       </c>
       <c r="C81">
-        <v>-151.5310397950598</v>
+        <v>-157.9285184301486</v>
       </c>
       <c r="D81">
-        <v>177.2079602049402</v>
+        <v>175.5514815698513</v>
       </c>
       <c r="E81">
-        <v>325.139</v>
+        <v>329.88</v>
       </c>
       <c r="F81">
-        <v>374.539</v>
+        <v>379.28</v>
       </c>
       <c r="G81">
         <v>45.8</v>
@@ -7929,37 +7929,37 @@
         <v>41.7</v>
       </c>
       <c r="M81">
-        <v>75.2074312</v>
+        <v>76.159424</v>
       </c>
       <c r="N81">
-        <v>-33.5074312</v>
+        <v>-34.459424</v>
       </c>
       <c r="O81">
-        <v>-8.3768578</v>
+        <v>-8.614856</v>
       </c>
       <c r="P81">
-        <v>-25.1305734</v>
+        <v>-25.844568</v>
       </c>
       <c r="Q81">
-        <v>-14.3305734</v>
+        <v>-15.044568</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2703381871382438</v>
+        <v>0.281565096495156</v>
       </c>
       <c r="T81">
-        <v>4.376667200032313</v>
+        <v>4.595500560033929</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1386166211724035</v>
+        <v>0.1368839134077485</v>
       </c>
       <c r="W81">
-        <v>0.1729657824685814</v>
+        <v>0.1733137101877241</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5544664846896141</v>
+        <v>0.5475356536309939</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1949639874492105</v>
+        <v>0.1965139874492105</v>
       </c>
       <c r="C82">
-        <v>-157.9285184301486</v>
+        <v>-164.2953154888851</v>
       </c>
       <c r="D82">
-        <v>175.5514815698513</v>
+        <v>173.925684511115</v>
       </c>
       <c r="E82">
-        <v>329.88</v>
+        <v>334.621</v>
       </c>
       <c r="F82">
-        <v>379.28</v>
+        <v>384.021</v>
       </c>
       <c r="G82">
         <v>45.8</v>
@@ -8011,37 +8011,37 @@
         <v>41.7</v>
       </c>
       <c r="M82">
-        <v>76.159424</v>
+        <v>77.1114168</v>
       </c>
       <c r="N82">
-        <v>-34.459424</v>
+        <v>-35.4114168</v>
       </c>
       <c r="O82">
-        <v>-8.614856</v>
+        <v>-8.852854199999999</v>
       </c>
       <c r="P82">
-        <v>-25.844568</v>
+        <v>-26.5585626</v>
       </c>
       <c r="Q82">
-        <v>-15.044568</v>
+        <v>-15.7585626</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.281565096495156</v>
+        <v>0.2939737857843747</v>
       </c>
       <c r="T82">
-        <v>4.595500560033929</v>
+        <v>4.83736901056203</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1368839134077485</v>
+        <v>0.1351939885508627</v>
       </c>
       <c r="W82">
-        <v>0.1733137101877241</v>
+        <v>0.1736530470989868</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5475356536309939</v>
+        <v>0.5407759542034507</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1965139874492105</v>
+        <v>0.1980639874492105</v>
       </c>
       <c r="C83">
-        <v>-164.2953154888851</v>
+        <v>-170.6322755832358</v>
       </c>
       <c r="D83">
-        <v>173.925684511115</v>
+        <v>172.3297244167642</v>
       </c>
       <c r="E83">
-        <v>334.621</v>
+        <v>339.362</v>
       </c>
       <c r="F83">
-        <v>384.021</v>
+        <v>388.762</v>
       </c>
       <c r="G83">
         <v>45.8</v>
@@ -8093,37 +8093,37 @@
         <v>41.7</v>
       </c>
       <c r="M83">
-        <v>77.1114168</v>
+        <v>78.0634096</v>
       </c>
       <c r="N83">
-        <v>-35.4114168</v>
+        <v>-36.3634096</v>
       </c>
       <c r="O83">
-        <v>-8.852854199999999</v>
+        <v>-9.090852399999999</v>
       </c>
       <c r="P83">
-        <v>-26.5585626</v>
+        <v>-27.2725572</v>
       </c>
       <c r="Q83">
-        <v>-15.7585626</v>
+        <v>-16.4725572</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2939737857843747</v>
+        <v>0.3077612183279511</v>
       </c>
       <c r="T83">
-        <v>4.83736901056203</v>
+        <v>5.106111733371033</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1351939885508627</v>
+        <v>0.1335452813734131</v>
       </c>
       <c r="W83">
-        <v>0.1736530470989868</v>
+        <v>0.1739841075002186</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5407759542034507</v>
+        <v>0.5341811254936526</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1980639874492105</v>
+        <v>0.1996139874492105</v>
       </c>
       <c r="C84">
-        <v>-170.6322755832358</v>
+        <v>-176.9402126060618</v>
       </c>
       <c r="D84">
-        <v>172.3297244167642</v>
+        <v>170.7627873939382</v>
       </c>
       <c r="E84">
-        <v>339.362</v>
+        <v>344.103</v>
       </c>
       <c r="F84">
-        <v>388.762</v>
+        <v>393.503</v>
       </c>
       <c r="G84">
         <v>45.8</v>
@@ -8175,37 +8175,37 @@
         <v>41.7</v>
       </c>
       <c r="M84">
-        <v>78.0634096</v>
+        <v>79.0154024</v>
       </c>
       <c r="N84">
-        <v>-36.3634096</v>
+        <v>-37.3154024</v>
       </c>
       <c r="O84">
-        <v>-9.090852399999999</v>
+        <v>-9.328850599999999</v>
       </c>
       <c r="P84">
-        <v>-27.2725572</v>
+        <v>-27.9865518</v>
       </c>
       <c r="Q84">
-        <v>-16.4725572</v>
+        <v>-17.1865518</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3077612183279511</v>
+        <v>0.323170701759007</v>
       </c>
       <c r="T84">
-        <v>5.106111733371033</v>
+        <v>5.40647124709874</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1335452813734131</v>
+        <v>0.1319363020797576</v>
       </c>
       <c r="W84">
-        <v>0.1739841075002186</v>
+        <v>0.1743071905423847</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5341811254936526</v>
+        <v>0.5277452083190303</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1996139874492105</v>
+        <v>0.2011639874492105</v>
       </c>
       <c r="C85">
-        <v>-176.9402126060618</v>
+        <v>-183.219911115127</v>
       </c>
       <c r="D85">
-        <v>170.7627873939382</v>
+        <v>169.224088884873</v>
       </c>
       <c r="E85">
-        <v>344.103</v>
+        <v>348.8440000000001</v>
       </c>
       <c r="F85">
-        <v>393.503</v>
+        <v>398.244</v>
       </c>
       <c r="G85">
         <v>45.8</v>
@@ -8257,37 +8257,37 @@
         <v>41.7</v>
       </c>
       <c r="M85">
-        <v>79.0154024</v>
+        <v>79.96739520000001</v>
       </c>
       <c r="N85">
-        <v>-37.3154024</v>
+        <v>-38.26739520000001</v>
       </c>
       <c r="O85">
-        <v>-9.328850599999999</v>
+        <v>-9.566848800000002</v>
       </c>
       <c r="P85">
-        <v>-27.9865518</v>
+        <v>-28.70054640000001</v>
       </c>
       <c r="Q85">
-        <v>-17.1865518</v>
+        <v>-17.90054640000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.323170701759007</v>
+        <v>0.3405063706189451</v>
       </c>
       <c r="T85">
-        <v>5.40647124709874</v>
+        <v>5.744375700042413</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1319363020797576</v>
+        <v>0.1303656318169033</v>
       </c>
       <c r="W85">
-        <v>0.1743071905423847</v>
+        <v>0.1746225811311658</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5277452083190303</v>
+        <v>0.5214625272676132</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2011639874492105</v>
+        <v>0.2027139874492105</v>
       </c>
       <c r="C86">
-        <v>-183.219911115127</v>
+        <v>-189.47212764295</v>
       </c>
       <c r="D86">
-        <v>169.2240888848729</v>
+        <v>167.7128723570499</v>
       </c>
       <c r="E86">
-        <v>348.844</v>
+        <v>353.585</v>
       </c>
       <c r="F86">
-        <v>398.244</v>
+        <v>402.985</v>
       </c>
       <c r="G86">
         <v>45.8</v>
@@ -8339,37 +8339,37 @@
         <v>41.7</v>
       </c>
       <c r="M86">
-        <v>79.9673952</v>
+        <v>80.919388</v>
       </c>
       <c r="N86">
-        <v>-38.2673952</v>
+        <v>-39.219388</v>
       </c>
       <c r="O86">
-        <v>-9.566848799999999</v>
+        <v>-9.804846999999999</v>
       </c>
       <c r="P86">
-        <v>-28.7005464</v>
+        <v>-29.414541</v>
       </c>
       <c r="Q86">
-        <v>-17.9005464</v>
+        <v>-18.614541</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3405063706189448</v>
+        <v>0.3601534619935412</v>
       </c>
       <c r="T86">
-        <v>5.744375700042409</v>
+        <v>6.127334080045236</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1303656318169033</v>
+        <v>0.1288319185014103</v>
       </c>
       <c r="W86">
-        <v>0.1746225811311658</v>
+        <v>0.1749305507649168</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5214625272676132</v>
+        <v>0.5153276740056414</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2027139874492105</v>
+        <v>0.2042639874492105</v>
       </c>
       <c r="C87">
-        <v>-189.47212764295</v>
+        <v>-195.6975919370924</v>
       </c>
       <c r="D87">
-        <v>167.7128723570499</v>
+        <v>166.2284080629075</v>
       </c>
       <c r="E87">
-        <v>353.585</v>
+        <v>358.326</v>
       </c>
       <c r="F87">
-        <v>402.985</v>
+        <v>407.7259999999999</v>
       </c>
       <c r="G87">
         <v>45.8</v>
@@ -8421,37 +8421,37 @@
         <v>41.7</v>
       </c>
       <c r="M87">
-        <v>80.919388</v>
+        <v>81.8713808</v>
       </c>
       <c r="N87">
-        <v>-39.219388</v>
+        <v>-40.17138079999999</v>
       </c>
       <c r="O87">
-        <v>-9.804846999999999</v>
+        <v>-10.0428452</v>
       </c>
       <c r="P87">
-        <v>-29.414541</v>
+        <v>-30.1285356</v>
       </c>
       <c r="Q87">
-        <v>-18.614541</v>
+        <v>-19.3285356</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3601534619935412</v>
+        <v>0.3826072807073655</v>
       </c>
       <c r="T87">
-        <v>6.127334080045236</v>
+        <v>6.565000800048468</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1288319185014103</v>
+        <v>0.1273338729374404</v>
       </c>
       <c r="W87">
-        <v>0.1749305507649168</v>
+        <v>0.175231358314162</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5153276740056414</v>
+        <v>0.5093354917497618</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2042639874492105</v>
+        <v>0.2058139874492105</v>
       </c>
       <c r="C88">
-        <v>-195.6975919370924</v>
+        <v>-201.8970081351572</v>
       </c>
       <c r="D88">
-        <v>166.2284080629075</v>
+        <v>164.7699918648428</v>
       </c>
       <c r="E88">
-        <v>358.326</v>
+        <v>363.067</v>
       </c>
       <c r="F88">
-        <v>407.7259999999999</v>
+        <v>412.467</v>
       </c>
       <c r="G88">
         <v>45.8</v>
@@ -8503,37 +8503,37 @@
         <v>41.7</v>
       </c>
       <c r="M88">
-        <v>81.8713808</v>
+        <v>82.8233736</v>
       </c>
       <c r="N88">
-        <v>-40.17138079999999</v>
+        <v>-41.12337359999999</v>
       </c>
       <c r="O88">
-        <v>-10.0428452</v>
+        <v>-10.2808434</v>
       </c>
       <c r="P88">
-        <v>-30.1285356</v>
+        <v>-30.8425302</v>
       </c>
       <c r="Q88">
-        <v>-19.3285356</v>
+        <v>-20.04253019999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3826072807073655</v>
+        <v>0.4085155330694706</v>
       </c>
       <c r="T88">
-        <v>6.565000800048468</v>
+        <v>7.070000861590658</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1273338729374404</v>
+        <v>0.1258702652025273</v>
       </c>
       <c r="W88">
-        <v>0.175231358314162</v>
+        <v>0.1755252507473325</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5093354917497618</v>
+        <v>0.5034810608101093</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2058139874492105</v>
+        <v>0.239024675362103</v>
       </c>
       <c r="C89">
-        <v>-201.8970081351572</v>
+        <v>-232.7109295078211</v>
       </c>
       <c r="D89">
-        <v>164.7699918648428</v>
+        <v>138.6970704921789</v>
       </c>
       <c r="E89">
-        <v>363.067</v>
+        <v>367.808</v>
       </c>
       <c r="F89">
-        <v>412.467</v>
+        <v>417.208</v>
       </c>
       <c r="G89">
         <v>45.8</v>
@@ -8585,45 +8585,45 @@
         <v>41.7</v>
       </c>
       <c r="M89">
-        <v>82.8233736</v>
+        <v>98.3776464</v>
       </c>
       <c r="N89">
-        <v>-41.12337359999999</v>
+        <v>-56.6776464</v>
       </c>
       <c r="O89">
-        <v>-10.2808434</v>
+        <v>-14.1694116</v>
       </c>
       <c r="P89">
-        <v>-30.8425302</v>
+        <v>-42.5082348</v>
       </c>
       <c r="Q89">
-        <v>-20.04253019999999</v>
+        <v>-31.7082348</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4085155330694706</v>
+        <v>0.4459142267660305</v>
       </c>
       <c r="T89">
-        <v>7.070000861590658</v>
+        <v>7.798971011888581</v>
       </c>
       <c r="U89">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1258702652025273</v>
+        <v>0.1059691950507976</v>
       </c>
       <c r="W89">
-        <v>0.1755252507473325</v>
+        <v>0.2108124638070219</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5034810608101093</v>
+        <v>0.4238767802031905</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.239024675362103</v>
+        <v>0.2409246753621029</v>
       </c>
       <c r="C90">
-        <v>-232.7109295078211</v>
+        <v>-238.6962740898463</v>
       </c>
       <c r="D90">
-        <v>138.6970704921789</v>
+        <v>137.4527259101537</v>
       </c>
       <c r="E90">
-        <v>367.808</v>
+        <v>372.549</v>
       </c>
       <c r="F90">
-        <v>417.208</v>
+        <v>421.949</v>
       </c>
       <c r="G90">
         <v>45.8</v>
@@ -8667,37 +8667,37 @@
         <v>41.7</v>
       </c>
       <c r="M90">
-        <v>98.3776464</v>
+        <v>99.49557419999999</v>
       </c>
       <c r="N90">
-        <v>-56.6776464</v>
+        <v>-57.79557419999999</v>
       </c>
       <c r="O90">
-        <v>-14.1694116</v>
+        <v>-14.44889355</v>
       </c>
       <c r="P90">
-        <v>-42.5082348</v>
+        <v>-43.34668065</v>
       </c>
       <c r="Q90">
-        <v>-31.7082348</v>
+        <v>-32.54668065</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4459142267660305</v>
+        <v>0.4822882473811241</v>
       </c>
       <c r="T90">
-        <v>7.798971011888581</v>
+        <v>8.507968376605724</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1059691950507976</v>
+        <v>0.1047785299378673</v>
       </c>
       <c r="W90">
-        <v>0.2108124638070219</v>
+        <v>0.2110932226406509</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4238767802031905</v>
+        <v>0.4191141197514694</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2409246753621029</v>
+        <v>0.2428246753621029</v>
       </c>
       <c r="C91">
-        <v>-238.6962740898463</v>
+        <v>-244.6594895053487</v>
       </c>
       <c r="D91">
-        <v>137.4527259101537</v>
+        <v>136.2305104946513</v>
       </c>
       <c r="E91">
-        <v>372.549</v>
+        <v>377.29</v>
       </c>
       <c r="F91">
-        <v>421.949</v>
+        <v>426.69</v>
       </c>
       <c r="G91">
         <v>45.8</v>
@@ -8749,37 +8749,37 @@
         <v>41.7</v>
       </c>
       <c r="M91">
-        <v>99.49557419999999</v>
+        <v>100.613502</v>
       </c>
       <c r="N91">
-        <v>-57.79557419999999</v>
+        <v>-58.91350199999999</v>
       </c>
       <c r="O91">
-        <v>-14.44889355</v>
+        <v>-14.7283755</v>
       </c>
       <c r="P91">
-        <v>-43.34668065</v>
+        <v>-44.1851265</v>
       </c>
       <c r="Q91">
-        <v>-32.54668065</v>
+        <v>-33.3851265</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4822882473811241</v>
+        <v>0.5259370721192366</v>
       </c>
       <c r="T91">
-        <v>8.507968376605724</v>
+        <v>9.358765214266297</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1047785299378673</v>
+        <v>0.1036143240496688</v>
       </c>
       <c r="W91">
-        <v>0.2110932226406509</v>
+        <v>0.2113677423890881</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4191141197514694</v>
+        <v>0.4144572961986752</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2428246753621029</v>
+        <v>0.244724675362103</v>
       </c>
       <c r="C92">
-        <v>-244.6594895053487</v>
+        <v>-250.6011608623843</v>
       </c>
       <c r="D92">
-        <v>136.2305104946513</v>
+        <v>135.0298391376157</v>
       </c>
       <c r="E92">
-        <v>377.29</v>
+        <v>382.031</v>
       </c>
       <c r="F92">
-        <v>426.69</v>
+        <v>431.431</v>
       </c>
       <c r="G92">
         <v>45.8</v>
@@ -8831,37 +8831,37 @@
         <v>41.7</v>
       </c>
       <c r="M92">
-        <v>100.613502</v>
+        <v>101.7314298</v>
       </c>
       <c r="N92">
-        <v>-58.91350199999999</v>
+        <v>-60.0314298</v>
       </c>
       <c r="O92">
-        <v>-14.7283755</v>
+        <v>-15.00785745</v>
       </c>
       <c r="P92">
-        <v>-44.1851265</v>
+        <v>-45.02357234999999</v>
       </c>
       <c r="Q92">
-        <v>-33.3851265</v>
+        <v>-34.22357235</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5259370721192366</v>
+        <v>0.5792856356880406</v>
       </c>
       <c r="T92">
-        <v>9.358765214266297</v>
+        <v>10.39862801585144</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1036143240496688</v>
+        <v>0.102475705104068</v>
       </c>
       <c r="W92">
-        <v>0.2113677423890881</v>
+        <v>0.2116362287364608</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4144572961986752</v>
+        <v>0.4099028204162722</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.244724675362103</v>
+        <v>0.246624675362103</v>
       </c>
       <c r="C93">
-        <v>-250.6011608623843</v>
+        <v>-256.521852821758</v>
       </c>
       <c r="D93">
-        <v>135.0298391376157</v>
+        <v>133.850147178242</v>
       </c>
       <c r="E93">
-        <v>382.031</v>
+        <v>386.772</v>
       </c>
       <c r="F93">
-        <v>431.431</v>
+        <v>436.172</v>
       </c>
       <c r="G93">
         <v>45.8</v>
@@ -8913,37 +8913,37 @@
         <v>41.7</v>
       </c>
       <c r="M93">
-        <v>101.7314298</v>
+        <v>102.8493576</v>
       </c>
       <c r="N93">
-        <v>-60.0314298</v>
+        <v>-61.14935759999999</v>
       </c>
       <c r="O93">
-        <v>-15.00785745</v>
+        <v>-15.2873394</v>
       </c>
       <c r="P93">
-        <v>-45.02357234999999</v>
+        <v>-45.86201819999999</v>
       </c>
       <c r="Q93">
-        <v>-34.22357235</v>
+        <v>-35.0620182</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5792856356880406</v>
+        <v>0.6459713401490459</v>
       </c>
       <c r="T93">
-        <v>10.39862801585144</v>
+        <v>11.69845651783288</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.102475705104068</v>
+        <v>0.1013618387442412</v>
       </c>
       <c r="W93">
-        <v>0.2116362287364608</v>
+        <v>0.2118988784241079</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4099028204162722</v>
+        <v>0.4054473549769649</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.246624675362103</v>
+        <v>0.2485246753621029</v>
       </c>
       <c r="C94">
-        <v>-256.521852821758</v>
+        <v>-262.4221104824773</v>
       </c>
       <c r="D94">
-        <v>133.850147178242</v>
+        <v>132.6908895175227</v>
       </c>
       <c r="E94">
-        <v>386.772</v>
+        <v>391.513</v>
       </c>
       <c r="F94">
-        <v>436.172</v>
+        <v>440.913</v>
       </c>
       <c r="G94">
         <v>45.8</v>
@@ -8995,37 +8995,37 @@
         <v>41.7</v>
       </c>
       <c r="M94">
-        <v>102.8493576</v>
+        <v>103.9672854</v>
       </c>
       <c r="N94">
-        <v>-61.14935759999999</v>
+        <v>-62.26728540000001</v>
       </c>
       <c r="O94">
-        <v>-15.2873394</v>
+        <v>-15.56682135</v>
       </c>
       <c r="P94">
-        <v>-45.86201819999999</v>
+        <v>-46.70046405000001</v>
       </c>
       <c r="Q94">
-        <v>-35.0620182</v>
+        <v>-35.90046405000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6459713401490459</v>
+        <v>0.731710103027481</v>
       </c>
       <c r="T94">
-        <v>11.69845651783288</v>
+        <v>13.369664591809</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1013618387442412</v>
+        <v>0.1002719264996795</v>
       </c>
       <c r="W94">
-        <v>0.2118988784241079</v>
+        <v>0.2121558797313756</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4054473549769649</v>
+        <v>0.4010877059987179</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2485246753621029</v>
+        <v>0.2504246753621029</v>
       </c>
       <c r="C95">
-        <v>-262.4221104824773</v>
+        <v>-268.3024602215885</v>
       </c>
       <c r="D95">
-        <v>132.6908895175227</v>
+        <v>131.5515397784115</v>
       </c>
       <c r="E95">
-        <v>391.513</v>
+        <v>396.254</v>
       </c>
       <c r="F95">
-        <v>440.913</v>
+        <v>445.654</v>
       </c>
       <c r="G95">
         <v>45.8</v>
@@ -9077,37 +9077,37 @@
         <v>41.7</v>
       </c>
       <c r="M95">
-        <v>103.9672854</v>
+        <v>105.0852132</v>
       </c>
       <c r="N95">
-        <v>-62.26728540000001</v>
+        <v>-63.3852132</v>
       </c>
       <c r="O95">
-        <v>-15.56682135</v>
+        <v>-15.8463033</v>
       </c>
       <c r="P95">
-        <v>-46.70046405000001</v>
+        <v>-47.53890989999999</v>
       </c>
       <c r="Q95">
-        <v>-35.90046405000001</v>
+        <v>-36.7389099</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.731710103027481</v>
+        <v>0.8460284535320615</v>
       </c>
       <c r="T95">
-        <v>13.369664591809</v>
+        <v>15.59794202377717</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1002719264996795</v>
+        <v>0.09920520387734248</v>
       </c>
       <c r="W95">
-        <v>0.2121558797313756</v>
+        <v>0.2124074129257227</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4010877059987179</v>
+        <v>0.3968208155093699</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2504246753621029</v>
+        <v>0.252324675362103</v>
       </c>
       <c r="C96">
-        <v>-268.3024602215885</v>
+        <v>-274.1634104911147</v>
       </c>
       <c r="D96">
-        <v>131.5515397784115</v>
+        <v>130.4315895088852</v>
       </c>
       <c r="E96">
-        <v>396.254</v>
+        <v>400.995</v>
       </c>
       <c r="F96">
-        <v>445.654</v>
+        <v>450.395</v>
       </c>
       <c r="G96">
         <v>45.8</v>
@@ -9159,37 +9159,37 @@
         <v>41.7</v>
       </c>
       <c r="M96">
-        <v>105.0852132</v>
+        <v>106.203141</v>
       </c>
       <c r="N96">
-        <v>-63.3852132</v>
+        <v>-64.503141</v>
       </c>
       <c r="O96">
-        <v>-15.8463033</v>
+        <v>-16.12578525</v>
       </c>
       <c r="P96">
-        <v>-47.53890989999999</v>
+        <v>-48.37735575</v>
       </c>
       <c r="Q96">
-        <v>-36.7389099</v>
+        <v>-37.57735575</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8460284535320615</v>
+        <v>1.006074144238474</v>
       </c>
       <c r="T96">
-        <v>15.59794202377717</v>
+        <v>18.71753042853262</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09920520387734248</v>
+        <v>0.09816093857337045</v>
       </c>
       <c r="W96">
-        <v>0.2124074129257227</v>
+        <v>0.2126536506843993</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3968208155093699</v>
+        <v>0.3926437542934818</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.252324675362103</v>
+        <v>0.2542246753621029</v>
       </c>
       <c r="C97">
-        <v>-274.1634104911147</v>
+        <v>-280.0054525746281</v>
       </c>
       <c r="D97">
-        <v>130.4315895088852</v>
+        <v>129.3305474253719</v>
       </c>
       <c r="E97">
-        <v>400.995</v>
+        <v>405.736</v>
       </c>
       <c r="F97">
-        <v>450.395</v>
+        <v>455.136</v>
       </c>
       <c r="G97">
         <v>45.8</v>
@@ -9241,37 +9241,37 @@
         <v>41.7</v>
       </c>
       <c r="M97">
-        <v>106.203141</v>
+        <v>107.3210688</v>
       </c>
       <c r="N97">
-        <v>-64.503141</v>
+        <v>-65.6210688</v>
       </c>
       <c r="O97">
-        <v>-16.12578525</v>
+        <v>-16.4052672</v>
       </c>
       <c r="P97">
-        <v>-48.37735575</v>
+        <v>-49.21580160000001</v>
       </c>
       <c r="Q97">
-        <v>-37.57735575</v>
+        <v>-38.41580160000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.006074144238474</v>
+        <v>1.246142680298093</v>
       </c>
       <c r="T97">
-        <v>18.71753042853262</v>
+        <v>23.39691303566578</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09816093857337045</v>
+        <v>0.09713842879656451</v>
       </c>
       <c r="W97">
-        <v>0.2126536506843993</v>
+        <v>0.2128947584897701</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3926437542934818</v>
+        <v>0.388553715186258</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2542246753621029</v>
+        <v>0.2561246753621029</v>
       </c>
       <c r="C98">
-        <v>-280.0054525746281</v>
+        <v>-285.8290613058244</v>
       </c>
       <c r="D98">
-        <v>129.3305474253719</v>
+        <v>128.2479386941756</v>
       </c>
       <c r="E98">
-        <v>405.736</v>
+        <v>410.477</v>
       </c>
       <c r="F98">
-        <v>455.136</v>
+        <v>459.877</v>
       </c>
       <c r="G98">
         <v>45.8</v>
@@ -9323,37 +9323,37 @@
         <v>41.7</v>
       </c>
       <c r="M98">
-        <v>107.3210688</v>
+        <v>108.4389966</v>
       </c>
       <c r="N98">
-        <v>-65.62106879999999</v>
+        <v>-66.73899659999999</v>
       </c>
       <c r="O98">
-        <v>-16.4052672</v>
+        <v>-16.68474915</v>
       </c>
       <c r="P98">
-        <v>-49.21580159999999</v>
+        <v>-50.05424744999999</v>
       </c>
       <c r="Q98">
-        <v>-38.41580159999999</v>
+        <v>-39.25424744999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.24614268029809</v>
+        <v>1.64625690706412</v>
       </c>
       <c r="T98">
-        <v>23.39691303566572</v>
+        <v>31.19588404755429</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09713842879656452</v>
+        <v>0.096137001695569</v>
       </c>
       <c r="W98">
-        <v>0.2128947584897701</v>
+        <v>0.2131308950001848</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.388553715186258</v>
+        <v>0.384548006782276</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2561246753621029</v>
+        <v>0.2580246753621029</v>
       </c>
       <c r="C99">
-        <v>-285.8290613058244</v>
+        <v>-291.6346957513059</v>
       </c>
       <c r="D99">
-        <v>128.2479386941756</v>
+        <v>127.183304248694</v>
       </c>
       <c r="E99">
-        <v>410.477</v>
+        <v>415.218</v>
       </c>
       <c r="F99">
-        <v>459.877</v>
+        <v>464.6179999999999</v>
       </c>
       <c r="G99">
         <v>45.8</v>
@@ -9405,37 +9405,37 @@
         <v>41.7</v>
       </c>
       <c r="M99">
-        <v>108.4389966</v>
+        <v>109.5569244</v>
       </c>
       <c r="N99">
-        <v>-66.73899659999999</v>
+        <v>-67.85692439999998</v>
       </c>
       <c r="O99">
-        <v>-16.68474915</v>
+        <v>-16.9642311</v>
       </c>
       <c r="P99">
-        <v>-50.05424744999999</v>
+        <v>-50.89269329999999</v>
       </c>
       <c r="Q99">
-        <v>-39.25424744999999</v>
+        <v>-40.09269329999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.64625690706412</v>
+        <v>2.44648536059618</v>
       </c>
       <c r="T99">
-        <v>31.19588404755429</v>
+        <v>46.79382607133144</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.096137001695569</v>
+        <v>0.09515601188234891</v>
       </c>
       <c r="W99">
-        <v>0.2131308950001848</v>
+        <v>0.2133622123981421</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.384548006782276</v>
+        <v>0.3806240475293957</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2580246753621029</v>
+        <v>0.259924675362103</v>
       </c>
       <c r="C100">
-        <v>-291.6346957513059</v>
+        <v>-297.4227998596364</v>
       </c>
       <c r="D100">
-        <v>127.183304248694</v>
+        <v>126.1362001403636</v>
       </c>
       <c r="E100">
-        <v>415.218</v>
+        <v>419.959</v>
       </c>
       <c r="F100">
-        <v>464.6179999999999</v>
+        <v>469.359</v>
       </c>
       <c r="G100">
         <v>45.8</v>
@@ -9487,37 +9487,37 @@
         <v>41.7</v>
       </c>
       <c r="M100">
-        <v>109.5569244</v>
+        <v>110.6748522</v>
       </c>
       <c r="N100">
-        <v>-67.85692439999998</v>
+        <v>-68.9748522</v>
       </c>
       <c r="O100">
-        <v>-16.9642311</v>
+        <v>-17.24371305</v>
       </c>
       <c r="P100">
-        <v>-50.89269329999999</v>
+        <v>-51.73113915</v>
       </c>
       <c r="Q100">
-        <v>-40.09269329999999</v>
+        <v>-40.93113915000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.44648536059618</v>
+        <v>4.84717072119236</v>
       </c>
       <c r="T100">
-        <v>46.79382607133144</v>
+        <v>93.58765214266288</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09515601188234891</v>
+        <v>0.09419484004515345</v>
       </c>
       <c r="W100">
-        <v>0.2133622123981421</v>
+        <v>0.2135888567173528</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3806240475293957</v>
+        <v>0.3767793601806139</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.259924675362103</v>
-      </c>
-      <c r="C101">
-        <v>-297.4227998596364</v>
-      </c>
-      <c r="D101">
-        <v>126.1362001403636</v>
-      </c>
-      <c r="E101">
-        <v>419.959</v>
-      </c>
-      <c r="F101">
-        <v>469.359</v>
-      </c>
-      <c r="G101">
-        <v>45.8</v>
-      </c>
-      <c r="H101">
-        <v>424.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>52.5</v>
-      </c>
-      <c r="K101">
-        <v>10.8</v>
-      </c>
-      <c r="L101">
-        <v>41.7</v>
-      </c>
-      <c r="M101">
-        <v>110.6748522</v>
-      </c>
-      <c r="N101">
-        <v>-68.9748522</v>
-      </c>
-      <c r="O101">
-        <v>-17.24371305</v>
-      </c>
-      <c r="P101">
-        <v>-51.73113915</v>
-      </c>
-      <c r="Q101">
-        <v>-40.93113915000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.84717072119236</v>
-      </c>
-      <c r="T101">
-        <v>93.58765214266288</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09419484004515345</v>
-      </c>
-      <c r="W101">
-        <v>0.2135888567173528</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3767793601806139</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
